--- a/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/P-S.xlsx
+++ b/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/P-S.xlsx
@@ -564,7 +564,7 @@
     </row>
     <row r="2" spans="1:31">
       <c r="A2">
-        <v>867.8110852</v>
+        <v>865.8865358</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>46.5068972989729</v>
+        <v>30.100533034046</v>
       </c>
       <c r="E2">
         <v>80</v>
@@ -585,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>97.45415635000001</v>
+        <v>92.56679652</v>
       </c>
       <c r="I2">
-        <v>0.4222869798</v>
+        <v>4.535522239</v>
       </c>
       <c r="J2">
-        <v>2.123556673</v>
+        <v>2.89768124</v>
       </c>
       <c r="K2">
         <v>80</v>
@@ -648,18 +648,18 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0.001862749698</v>
+        <v>0.002086591718</v>
       </c>
       <c r="AD2">
-        <v>-0.001662501052</v>
+        <v>-0.001903580404</v>
       </c>
       <c r="AE2">
-        <v>-0.0002002486456</v>
+        <v>-0.0001830113139</v>
       </c>
     </row>
     <row r="3" spans="1:31">
       <c r="A3">
-        <v>852.5175211</v>
+        <v>852.629127</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>58.3574190749991</v>
+        <v>29.7322864234083</v>
       </c>
       <c r="E3">
         <v>79</v>
@@ -680,13 +680,13 @@
         <v>5</v>
       </c>
       <c r="H3">
-        <v>96.91084273</v>
+        <v>90.16413713999999</v>
       </c>
       <c r="I3">
-        <v>0.3181203562</v>
+        <v>6.166025316</v>
       </c>
       <c r="J3">
-        <v>2.771036911</v>
+        <v>3.669837545</v>
       </c>
       <c r="K3">
         <v>79</v>
@@ -743,13 +743,13 @@
         <v>0</v>
       </c>
       <c r="AC3">
-        <v>0.001523911934</v>
+        <v>0.001878392915</v>
       </c>
       <c r="AD3">
-        <v>-0.00133427461</v>
+        <v>-0.001654595914</v>
       </c>
       <c r="AE3">
-        <v>-0.0001896373237</v>
+        <v>-0.0002237970015</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>23.8290444498079</v>
+        <v>23.9206215583247</v>
       </c>
       <c r="E4">
         <v>83</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5">
-        <v>886.8558494</v>
+        <v>885.8519305999999</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>25.3700389983009</v>
+        <v>24.8430444051961</v>
       </c>
       <c r="E5">
         <v>82</v>
@@ -867,13 +867,13 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>98.2916931</v>
+        <v>96.84160172999999</v>
       </c>
       <c r="I5">
-        <v>1.210306284</v>
+        <v>2.393280497</v>
       </c>
       <c r="J5">
-        <v>0.4980006161</v>
+        <v>0.7651177772</v>
       </c>
       <c r="K5">
         <v>82</v>
@@ -930,18 +930,18 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>0.003188654571</v>
+        <v>0.002980824863</v>
       </c>
       <c r="AD5">
-        <v>-0.003090400364</v>
+        <v>-0.002933655957</v>
       </c>
       <c r="AE5">
-        <v>-9.825420733E-05</v>
+        <v>-4.716890673E-05</v>
       </c>
     </row>
     <row r="6" spans="1:31">
       <c r="A6">
-        <v>883.5148195</v>
+        <v>881.3624538</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>30.7280955282988</v>
+        <v>27.1897392767073</v>
       </c>
       <c r="E6">
         <v>81</v>
@@ -962,13 +962,13 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>98.16694318</v>
+        <v>95.52771933</v>
       </c>
       <c r="I6">
-        <v>0.8425009018</v>
+        <v>2.998729687</v>
       </c>
       <c r="J6">
-        <v>0.9905559197</v>
+        <v>1.473550986</v>
       </c>
       <c r="K6">
         <v>81</v>
@@ -1025,18 +1025,18 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>0.002771648599</v>
+        <v>0.002666973452</v>
       </c>
       <c r="AD6">
-        <v>-0.002608674466</v>
+        <v>-0.002570342804</v>
       </c>
       <c r="AE6">
-        <v>-0.000162974133</v>
+        <v>-9.663064828E-05</v>
       </c>
     </row>
     <row r="7" spans="1:31">
       <c r="A7">
-        <v>875.5501283</v>
+        <v>873.0525294</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>39.6834145995786</v>
+        <v>29.7456972139706</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -1057,13 +1057,13 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>97.86067989999999</v>
+        <v>93.90521368</v>
       </c>
       <c r="I7">
-        <v>0.6167286238</v>
+        <v>3.895695364</v>
       </c>
       <c r="J7">
-        <v>1.52259148</v>
+        <v>2.199090957</v>
       </c>
       <c r="K7">
         <v>80</v>
@@ -1120,18 +1120,18 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>0.002232218921</v>
+        <v>0.002335046159</v>
       </c>
       <c r="AD7">
-        <v>-0.0020475803</v>
+        <v>-0.002200571437</v>
       </c>
       <c r="AE7">
-        <v>-0.0001846386208</v>
+        <v>-0.0001344747226</v>
       </c>
     </row>
     <row r="8" spans="1:31">
       <c r="A8">
-        <v>863.3160764</v>
+        <v>861.7836263</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>51.0754036990057</v>
+        <v>30.6809727118005</v>
       </c>
       <c r="E8">
         <v>79</v>
@@ -1152,13 +1152,13 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>97.42208451</v>
+        <v>91.77635863</v>
       </c>
       <c r="I8">
-        <v>0.461984779</v>
+        <v>5.257438597</v>
       </c>
       <c r="J8">
-        <v>2.115930714</v>
+        <v>2.966202771</v>
       </c>
       <c r="K8">
         <v>79</v>
@@ -1215,18 +1215,18 @@
         <v>0</v>
       </c>
       <c r="AC8">
-        <v>0.00178906772</v>
+        <v>0.002081925037</v>
       </c>
       <c r="AD8">
-        <v>-0.001606104266</v>
+        <v>-0.001913483416</v>
       </c>
       <c r="AE8">
-        <v>-0.0001829634543</v>
+        <v>-0.0001684416216</v>
       </c>
     </row>
     <row r="9" spans="1:31">
       <c r="A9">
-        <v>847.3055821</v>
+        <v>848.5058801</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>63.6994559446445</v>
+        <v>28.645956858001</v>
       </c>
       <c r="E9">
         <v>78</v>
@@ -1247,13 +1247,13 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>96.87412077</v>
+        <v>88.99454163</v>
       </c>
       <c r="I9">
-        <v>0.3474204992</v>
+        <v>7.244629499</v>
       </c>
       <c r="J9">
-        <v>2.778458727</v>
+        <v>3.760828871</v>
       </c>
       <c r="K9">
         <v>78</v>
@@ -1310,13 +1310,13 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0.001470224503</v>
+        <v>0.001920936991</v>
       </c>
       <c r="AD9">
-        <v>-0.00129718348</v>
+        <v>-0.001704434375</v>
       </c>
       <c r="AE9">
-        <v>-0.0001730410229</v>
+        <v>-0.0002165026157</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25.703027253658</v>
+        <v>25.8122689957507</v>
       </c>
       <c r="E10">
         <v>82</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="11" spans="1:31">
       <c r="A11">
-        <v>883.6037007</v>
+        <v>882.4311735</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>27.6486157383603</v>
+        <v>26.954400754745</v>
       </c>
       <c r="E11">
         <v>81</v>
@@ -1434,13 +1434,13 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>98.20905042</v>
+        <v>96.62490127</v>
       </c>
       <c r="I11">
-        <v>1.308137132</v>
+        <v>2.608074843</v>
       </c>
       <c r="J11">
-        <v>0.482812445</v>
+        <v>0.7670238843</v>
       </c>
       <c r="K11">
         <v>81</v>
@@ -1497,18 +1497,18 @@
         <v>0</v>
       </c>
       <c r="AC11">
-        <v>0.003089511527</v>
+        <v>0.002892729354</v>
       </c>
       <c r="AD11">
-        <v>-0.002996660325</v>
+        <v>-0.002849602408</v>
       </c>
       <c r="AE11">
-        <v>-9.285120216E-05</v>
+        <v>-4.312694676E-05</v>
       </c>
     </row>
     <row r="12" spans="1:31">
       <c r="A12">
-        <v>914.8608159</v>
+        <v>914.668193</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>7.44036109212552</v>
+        <v>7.33487712905267</v>
       </c>
       <c r="E12">
         <v>95</v>
@@ -1529,13 +1529,13 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>97.55612173999999</v>
+        <v>97.40935626</v>
       </c>
       <c r="I12">
-        <v>0.01757244458</v>
+        <v>0.1281751927</v>
       </c>
       <c r="J12">
-        <v>2.426305819</v>
+        <v>2.462468547</v>
       </c>
       <c r="K12">
         <v>95</v>
@@ -1592,18 +1592,18 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>0.001708869707</v>
+        <v>0.001633972392</v>
       </c>
       <c r="AD12">
-        <v>-0.0006569099863</v>
+        <v>-0.0005913340098</v>
       </c>
       <c r="AE12">
-        <v>-0.00105195972</v>
+        <v>-0.001042638382</v>
       </c>
     </row>
     <row r="13" spans="1:31">
       <c r="A13">
-        <v>879.9674831</v>
+        <v>877.6594505</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>33.7763401608958</v>
+        <v>29.2732502988533</v>
       </c>
       <c r="E13">
         <v>80</v>
@@ -1624,13 +1624,13 @@
         <v>2</v>
       </c>
       <c r="H13">
-        <v>98.11379047</v>
+        <v>95.1720005</v>
       </c>
       <c r="I13">
-        <v>0.9152152419</v>
+        <v>3.335698681</v>
       </c>
       <c r="J13">
-        <v>0.9709942902000001</v>
+        <v>1.492300823</v>
       </c>
       <c r="K13">
         <v>80</v>
@@ -1687,18 +1687,18 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0.002659320599</v>
+        <v>0.002587356765</v>
       </c>
       <c r="AD13">
-        <v>-0.002508253092</v>
+        <v>-0.002500789718</v>
       </c>
       <c r="AE13">
-        <v>-0.0001510675069</v>
+        <v>-8.656704661E-05</v>
       </c>
     </row>
     <row r="14" spans="1:31">
       <c r="A14">
-        <v>871.4906359</v>
+        <v>869.0642319999999</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>43.6631294349</v>
+        <v>31.2081359371606</v>
       </c>
       <c r="E14">
         <v>79</v>
@@ -1719,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="H14">
-        <v>97.82136016</v>
+        <v>93.31940978999999</v>
       </c>
       <c r="I14">
-        <v>0.6720736336000001</v>
+        <v>4.435592761</v>
       </c>
       <c r="J14">
-        <v>1.506566209</v>
+        <v>2.244997452</v>
       </c>
       <c r="K14">
         <v>79</v>
@@ -1782,18 +1782,18 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0.002136591043</v>
+        <v>0.002292437247</v>
       </c>
       <c r="AD14">
-        <v>-0.001967063408</v>
+        <v>-0.002171584977</v>
       </c>
       <c r="AE14">
-        <v>-0.0001695276345</v>
+        <v>-0.0001208522697</v>
       </c>
     </row>
     <row r="15" spans="1:31">
       <c r="A15">
-        <v>858.5927128</v>
+        <v>857.6347721</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>55.9747597275661</v>
+        <v>30.7254085499116</v>
       </c>
       <c r="E15">
         <v>78</v>
@@ -1814,13 +1814,13 @@
         <v>4</v>
       </c>
       <c r="H15">
-        <v>97.38615846</v>
+        <v>90.84583101</v>
       </c>
       <c r="I15">
-        <v>0.5037987195</v>
+        <v>6.11227018</v>
       </c>
       <c r="J15">
-        <v>2.110042823</v>
+        <v>3.041898807</v>
       </c>
       <c r="K15">
         <v>78</v>
@@ -1877,18 +1877,18 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0.001716719938</v>
+        <v>0.002091034021</v>
       </c>
       <c r="AD15">
-        <v>-0.001549364436</v>
+        <v>-0.001935091583</v>
       </c>
       <c r="AE15">
-        <v>-0.0001673555022</v>
+        <v>-0.0001559424383</v>
       </c>
     </row>
     <row r="16" spans="1:31">
       <c r="A16">
-        <v>841.8252041</v>
+        <v>844.4551729999999</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>69.3977868661764</v>
+        <v>26.829157017715</v>
       </c>
       <c r="E16">
         <v>77</v>
@@ -1909,13 +1909,13 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>96.83364161</v>
+        <v>87.63329965</v>
       </c>
       <c r="I16">
-        <v>0.3780461164</v>
+        <v>8.511737223000001</v>
       </c>
       <c r="J16">
-        <v>2.788312273</v>
+        <v>3.854963122</v>
       </c>
       <c r="K16">
         <v>77</v>
@@ -1972,13 +1972,13 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>0.001417092027</v>
+        <v>0.001984835575</v>
       </c>
       <c r="AD16">
-        <v>-0.001259077244</v>
+        <v>-0.001771096375</v>
       </c>
       <c r="AE16">
-        <v>-0.0001580147828</v>
+        <v>-0.0002137392</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>27.6649090592803</v>
+        <v>27.7924590177788</v>
       </c>
       <c r="E17">
         <v>81</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="18" spans="1:31">
       <c r="A18">
-        <v>880.2506947000001</v>
+        <v>878.9087585</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>30.0870762062494</v>
+        <v>29.1563658336065</v>
       </c>
       <c r="E18">
         <v>80</v>
@@ -2096,13 +2096,13 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>98.12096517000001</v>
+        <v>96.38913243</v>
       </c>
       <c r="I18">
-        <v>1.410725401</v>
+        <v>2.84044129</v>
       </c>
       <c r="J18">
-        <v>0.4683094279</v>
+        <v>0.7704262848</v>
       </c>
       <c r="K18">
         <v>80</v>
@@ -2159,18 +2159,18 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>0.002988371663</v>
+        <v>0.002805409442</v>
       </c>
       <c r="AD18">
-        <v>-0.002900688049</v>
+        <v>-0.002766117388</v>
       </c>
       <c r="AE18">
-        <v>-8.768361407E-05</v>
+        <v>-3.929205392E-05</v>
       </c>
     </row>
     <row r="19" spans="1:31">
       <c r="A19">
-        <v>876.2738879</v>
+        <v>873.8388009</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>37.0609126246858</v>
+        <v>31.338351566083</v>
       </c>
       <c r="E19">
         <v>79</v>
@@ -2191,13 +2191,13 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>98.05570716</v>
+        <v>94.76885009</v>
       </c>
       <c r="I19">
-        <v>0.9918647816</v>
+        <v>3.71618448</v>
       </c>
       <c r="J19">
-        <v>0.9524280585</v>
+        <v>1.514965432</v>
       </c>
       <c r="K19">
         <v>79</v>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>0.002548312114</v>
+        <v>0.002512516272</v>
       </c>
       <c r="AD19">
-        <v>-0.002408223155</v>
+        <v>-0.002435246837</v>
       </c>
       <c r="AE19">
-        <v>-0.0001400889591</v>
+        <v>-7.726943571E-05</v>
       </c>
     </row>
     <row r="20" spans="1:31">
       <c r="A20">
-        <v>867.2366693</v>
+        <v>864.98124</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>47.9443209140938</v>
+        <v>32.3649624295637</v>
       </c>
       <c r="E20">
         <v>78</v>
@@ -2286,13 +2286,13 @@
         <v>3</v>
       </c>
       <c r="H20">
-        <v>97.77763503</v>
+        <v>92.63371128999999</v>
       </c>
       <c r="I20">
-        <v>0.7305279055</v>
+        <v>5.068579638</v>
       </c>
       <c r="J20">
-        <v>1.491837061</v>
+        <v>2.297709072</v>
       </c>
       <c r="K20">
         <v>78</v>
@@ -2349,18 +2349,18 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0.002043313687</v>
+        <v>0.002259664025</v>
       </c>
       <c r="AD20">
-        <v>-0.001887504178</v>
+        <v>-0.002151238215</v>
       </c>
       <c r="AE20">
-        <v>-0.0001558095092</v>
+        <v>-0.0001084258094</v>
       </c>
     </row>
     <row r="21" spans="1:31">
       <c r="A21">
-        <v>853.6291827</v>
+        <v>853.4749519</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>61.2208028521706</v>
+        <v>30.0962579673601</v>
       </c>
       <c r="E21">
         <v>77</v>
@@ -2381,13 +2381,13 @@
         <v>4</v>
       </c>
       <c r="H21">
-        <v>97.34620663</v>
+        <v>89.74497993999999</v>
       </c>
       <c r="I21">
-        <v>0.5478437852</v>
+        <v>7.130389901</v>
       </c>
       <c r="J21">
-        <v>2.105949585</v>
+        <v>3.124630159</v>
       </c>
       <c r="K21">
         <v>77</v>
@@ -2444,27 +2444,21 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0.001646102747</v>
+        <v>0.002119026005</v>
       </c>
       <c r="AD21">
-        <v>-0.00149287194</v>
+        <v>-0.001973499895</v>
       </c>
       <c r="AE21">
-        <v>-0.0001532308077</v>
+        <v>-0.0001455261106</v>
       </c>
     </row>
     <row r="22" spans="1:31">
       <c r="A22">
-        <v>836.0641664</v>
+        <v>842.8625087</v>
       </c>
       <c r="B22">
         <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>75.4660468518739</v>
       </c>
       <c r="E22">
         <v>76</v>
@@ -2476,13 +2470,13 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>96.78925568</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.4100153802</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2.800728944</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>76</v>
@@ -2494,13 +2488,13 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>62.54235303</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>28.42537001</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>9.032276954</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -2539,18 +2533,18 @@
         <v>0</v>
       </c>
       <c r="AC22">
-        <v>0.00136487437</v>
+        <v>-0.00136677263</v>
       </c>
       <c r="AD22">
-        <v>-0.00122049296</v>
+        <v>0.0009572504025</v>
       </c>
       <c r="AE22">
-        <v>-0.0001443814098</v>
+        <v>0.0004095222274</v>
       </c>
     </row>
     <row r="23" spans="1:31">
       <c r="A23">
-        <v>905.8250571999999</v>
+        <v>905.5462169</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2559,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>11.6168037934998</v>
+        <v>11.4640322253561</v>
       </c>
       <c r="E23">
         <v>94</v>
@@ -2571,19 +2565,19 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>97.09070939999999</v>
+        <v>96.92184338</v>
       </c>
       <c r="I23">
-        <v>0.01316915537</v>
+        <v>0.1426029345</v>
       </c>
       <c r="J23">
-        <v>2.896121443</v>
+        <v>2.93555369</v>
       </c>
       <c r="K23">
         <v>94</v>
       </c>
       <c r="L23">
-        <v>0.9999999999</v>
+        <v>1</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2634,13 +2628,13 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>0.001325457152</v>
+        <v>0.001270072806</v>
       </c>
       <c r="AD23">
-        <v>-0.0004232615806</v>
+        <v>-0.0003727291189</v>
       </c>
       <c r="AE23">
-        <v>-0.0009021955717</v>
+        <v>-0.0008973436871</v>
       </c>
     </row>
     <row r="24" spans="1:31">
@@ -2654,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>29.7220585107844</v>
+        <v>29.8701403114877</v>
       </c>
       <c r="E24">
         <v>80</v>
@@ -2737,7 +2731,7 @@
     </row>
     <row r="25" spans="1:31">
       <c r="A25">
-        <v>876.788547</v>
+        <v>875.2793463</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2746,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>32.6983760901535</v>
+        <v>31.444807968742</v>
       </c>
       <c r="E25">
         <v>79</v>
@@ -2758,13 +2752,13 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>98.02700110000001</v>
+        <v>96.130994</v>
       </c>
       <c r="I25">
-        <v>1.518533697</v>
+        <v>3.093522631</v>
       </c>
       <c r="J25">
-        <v>0.4544652046</v>
+        <v>0.7754833738</v>
       </c>
       <c r="K25">
         <v>79</v>
@@ -2821,18 +2815,18 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0.002885975291</v>
+        <v>0.002719347123</v>
       </c>
       <c r="AD25">
-        <v>-0.002803228639</v>
+        <v>-0.002683712901</v>
       </c>
       <c r="AE25">
-        <v>-8.27466519E-05</v>
+        <v>-3.563422233E-05</v>
       </c>
     </row>
     <row r="26" spans="1:31">
       <c r="A26">
-        <v>872.4239162</v>
+        <v>869.9009834</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2841,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>40.5975434160165</v>
+        <v>33.3313284362681</v>
       </c>
       <c r="E26">
         <v>78</v>
@@ -2853,13 +2847,13 @@
         <v>2</v>
       </c>
       <c r="H26">
-        <v>97.9923764</v>
+        <v>94.30730298</v>
       </c>
       <c r="I26">
-        <v>1.072787751</v>
+        <v>4.150576613</v>
       </c>
       <c r="J26">
-        <v>0.9348358453</v>
+        <v>1.542120406</v>
       </c>
       <c r="K26">
         <v>78</v>
@@ -2916,18 +2910,18 @@
         <v>0</v>
       </c>
       <c r="AC26">
-        <v>0.002439239241</v>
+        <v>0.002443512506</v>
       </c>
       <c r="AD26">
-        <v>-0.00230928229</v>
+        <v>-0.002374916181</v>
       </c>
       <c r="AE26">
-        <v>-0.0001299569512</v>
+        <v>-6.859632515E-05</v>
       </c>
     </row>
     <row r="27" spans="1:31">
       <c r="A27">
-        <v>862.7768656</v>
+        <v>860.8209218</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2936,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>52.5432219594912</v>
+        <v>33.0833128804301</v>
       </c>
       <c r="E27">
         <v>77</v>
@@ -2948,13 +2942,13 @@
         <v>3</v>
       </c>
       <c r="H27">
-        <v>97.72926474</v>
+        <v>91.82219938</v>
       </c>
       <c r="I27">
-        <v>0.7923228328</v>
+        <v>5.819757038</v>
       </c>
       <c r="J27">
-        <v>1.478412432</v>
+        <v>2.358043581</v>
       </c>
       <c r="K27">
         <v>77</v>
@@ -3011,18 +3005,18 @@
         <v>0</v>
       </c>
       <c r="AC27">
-        <v>0.001952755488</v>
+        <v>0.00223983041</v>
       </c>
       <c r="AD27">
-        <v>-0.001809422332</v>
+        <v>-0.002142841261</v>
       </c>
       <c r="AE27">
-        <v>-0.0001433331566</v>
+        <v>-9.698914865E-05</v>
       </c>
     </row>
     <row r="28" spans="1:31">
       <c r="A28">
-        <v>848.4132998</v>
+        <v>849.3503163</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3031,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>66.82943848041729</v>
+        <v>28.6659418567329</v>
       </c>
       <c r="E28">
         <v>76</v>
@@ -3043,13 +3037,13 @@
         <v>4</v>
       </c>
       <c r="H28">
-        <v>97.30204406</v>
+        <v>88.44064613</v>
       </c>
       <c r="I28">
-        <v>0.5942397185</v>
+        <v>8.345818267</v>
       </c>
       <c r="J28">
-        <v>2.103716219</v>
+        <v>3.213535602</v>
       </c>
       <c r="K28">
         <v>76</v>
@@ -3106,27 +3100,21 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <v>0.001577503133</v>
+        <v>0.002173019547</v>
       </c>
       <c r="AD28">
-        <v>-0.001437081511</v>
+        <v>-0.002035662425</v>
       </c>
       <c r="AE28">
-        <v>-0.0001404216219</v>
+        <v>-0.000137357122</v>
       </c>
     </row>
     <row r="29" spans="1:31">
       <c r="A29">
-        <v>830.0099118000001</v>
+        <v>845.7744804</v>
       </c>
       <c r="B29">
         <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>81.9175831430893</v>
       </c>
       <c r="E29">
         <v>75</v>
@@ -3138,13 +3126,13 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>96.7408071</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>0.4433364279</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>2.815856475</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>75</v>
@@ -3156,13 +3144,13 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>62.54235303</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>28.42537001</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>9.032276954</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -3201,13 +3189,13 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>0.001313842569</v>
+        <v>-0.001310317936</v>
       </c>
       <c r="AD29">
-        <v>-0.001181856535</v>
+        <v>0.0008861957421</v>
       </c>
       <c r="AE29">
-        <v>-0.0001319860336</v>
+        <v>0.0004241221941</v>
       </c>
     </row>
     <row r="30" spans="1:31">
@@ -3221,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>2.33418159955285</v>
+        <v>2.32903808338768</v>
       </c>
       <c r="E30">
         <v>98</v>
@@ -3304,7 +3292,7 @@
     </row>
     <row r="31" spans="1:31">
       <c r="A31">
-        <v>928.3464832</v>
+        <v>928.5190787</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3313,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2.53663703754787</v>
+        <v>2.31057763554096</v>
       </c>
       <c r="E31">
         <v>97</v>
@@ -3325,13 +3313,13 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>99.0592977</v>
+        <v>98.91554183</v>
       </c>
       <c r="I31">
-        <v>0.1128308441</v>
+        <v>0.2219654053</v>
       </c>
       <c r="J31">
-        <v>0.8278714523</v>
+        <v>0.8624927605</v>
       </c>
       <c r="K31">
         <v>97</v>
@@ -3388,18 +3376,18 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0.004000667595</v>
+        <v>0.004075242287</v>
       </c>
       <c r="AD31">
-        <v>-0.003666446294</v>
+        <v>-0.003782945265</v>
       </c>
       <c r="AE31">
-        <v>-0.0003342213019</v>
+        <v>-0.0002922970228</v>
       </c>
     </row>
     <row r="32" spans="1:31">
       <c r="A32">
-        <v>925.1495465</v>
+        <v>925.1789011</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -3408,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>3.49578853155141</v>
+        <v>3.25292471135689</v>
       </c>
       <c r="E32">
         <v>96</v>
@@ -3420,13 +3408,13 @@
         <v>2</v>
       </c>
       <c r="H32">
-        <v>98.506506</v>
+        <v>98.29292712</v>
       </c>
       <c r="I32">
-        <v>0.07216648031</v>
+        <v>0.2326272744</v>
       </c>
       <c r="J32">
-        <v>1.421327522</v>
+        <v>1.474445604</v>
       </c>
       <c r="K32">
         <v>96</v>
@@ -3483,18 +3471,18 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0.003552865436</v>
+        <v>0.003485090952</v>
       </c>
       <c r="AD32">
-        <v>-0.002732956444</v>
+        <v>-0.002686641676</v>
       </c>
       <c r="AE32">
-        <v>-0.0008199089918</v>
+        <v>-0.0007984492761999999</v>
       </c>
     </row>
     <row r="33" spans="1:31">
       <c r="A33">
-        <v>919.8363282</v>
+        <v>919.644916</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3503,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>5.55342178776782</v>
+        <v>5.34924035845983</v>
       </c>
       <c r="E33">
         <v>95</v>
@@ -3515,13 +3503,13 @@
         <v>3</v>
       </c>
       <c r="H33">
-        <v>98.02877952</v>
+        <v>97.76929941</v>
       </c>
       <c r="I33">
-        <v>0.04970722423</v>
+        <v>0.2446011549</v>
       </c>
       <c r="J33">
-        <v>1.921513258</v>
+        <v>1.986099439</v>
       </c>
       <c r="K33">
         <v>95</v>
@@ -3578,18 +3566,18 @@
         <v>0</v>
       </c>
       <c r="AC33">
-        <v>0.002707753063</v>
+        <v>0.002570444079</v>
       </c>
       <c r="AD33">
-        <v>-0.001743797504</v>
+        <v>-0.001629539461</v>
       </c>
       <c r="AE33">
-        <v>-0.0009639555589</v>
+        <v>-0.0009409046178</v>
       </c>
     </row>
     <row r="34" spans="1:31">
       <c r="A34">
-        <v>912.5914735</v>
+        <v>912.1927576</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3598,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>8.82039623121374</v>
+        <v>8.58677303283331</v>
       </c>
       <c r="E34">
         <v>94</v>
@@ -3610,13 +3598,13 @@
         <v>4</v>
       </c>
       <c r="H34">
-        <v>97.56837173</v>
+        <v>97.26640159999999</v>
       </c>
       <c r="I34">
-        <v>0.03604806278</v>
+        <v>0.2650178951</v>
       </c>
       <c r="J34">
-        <v>2.39558021</v>
+        <v>2.4685805</v>
       </c>
       <c r="K34">
         <v>94</v>
@@ -3673,18 +3661,18 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>0.002012918866</v>
+        <v>0.001893388027</v>
       </c>
       <c r="AD34">
-        <v>-0.00110798546</v>
+        <v>-0.001005780899</v>
       </c>
       <c r="AE34">
-        <v>-0.000904933406</v>
+        <v>-0.0008876071278</v>
       </c>
     </row>
     <row r="35" spans="1:31">
       <c r="A35">
-        <v>903.3849788</v>
+        <v>902.8274031</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3693,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>13.2503492345247</v>
+        <v>12.8796816922913</v>
       </c>
       <c r="E35">
         <v>93</v>
@@ -3705,13 +3693,13 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>97.09719735</v>
+        <v>96.74632846999999</v>
       </c>
       <c r="I35">
-        <v>0.02705600425</v>
+        <v>0.2978881155</v>
       </c>
       <c r="J35">
-        <v>2.875746647</v>
+        <v>2.955783414</v>
       </c>
       <c r="K35">
         <v>93</v>
@@ -3768,13 +3756,13 @@
         <v>0</v>
       </c>
       <c r="AC35">
-        <v>0.001540574441</v>
+        <v>0.001449950884</v>
       </c>
       <c r="AD35">
-        <v>-0.0007419077836</v>
+        <v>-0.0006588148041</v>
       </c>
       <c r="AE35">
-        <v>-0.0007986666575</v>
+        <v>-0.0007911360795</v>
       </c>
     </row>
     <row r="36" spans="1:31">
@@ -3788,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>3.53965886756807</v>
+        <v>3.53572278155424</v>
       </c>
       <c r="E36">
         <v>97</v>
@@ -3871,7 +3859,7 @@
     </row>
     <row r="37" spans="1:31">
       <c r="A37">
-        <v>925.7908736000001</v>
+        <v>926.0124954</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3880,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>3.75199814216132</v>
+        <v>3.45325990597862</v>
       </c>
       <c r="E37">
         <v>96</v>
@@ -3892,13 +3880,13 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>99.02983539</v>
+        <v>98.81435944</v>
       </c>
       <c r="I37">
-        <v>0.1713259976</v>
+        <v>0.3355468365</v>
       </c>
       <c r="J37">
-        <v>0.7988386169</v>
+        <v>0.8500937213999999</v>
       </c>
       <c r="K37">
         <v>96</v>
@@ -3955,13 +3943,13 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>0.003996433768</v>
+        <v>0.004027921194</v>
       </c>
       <c r="AD37">
-        <v>-0.003731164434</v>
+        <v>-0.003813481811</v>
       </c>
       <c r="AE37">
-        <v>-0.0002652693346</v>
+        <v>-0.0002144393824</v>
       </c>
     </row>
     <row r="38" spans="1:31">
@@ -3975,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0.107372025206244</v>
+        <v>0.107364381953774</v>
       </c>
       <c r="E38">
         <v>99</v>
@@ -4058,7 +4046,7 @@
     </row>
     <row r="39" spans="1:31">
       <c r="A39">
-        <v>922.777284</v>
+        <v>922.7787752</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -4067,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>4.69395532143474</v>
+        <v>4.37471646524903</v>
       </c>
       <c r="E39">
         <v>95</v>
@@ -4079,13 +4067,13 @@
         <v>2</v>
       </c>
       <c r="H39">
-        <v>98.50620154000001</v>
+        <v>98.18276514999999</v>
       </c>
       <c r="I39">
-        <v>0.1102300427</v>
+        <v>0.3543167759</v>
       </c>
       <c r="J39">
-        <v>1.383568421</v>
+        <v>1.462918075</v>
       </c>
       <c r="K39">
         <v>95</v>
@@ -4142,18 +4130,18 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0.003703265552</v>
+        <v>0.00360589325</v>
       </c>
       <c r="AD39">
-        <v>-0.003052372277</v>
+        <v>-0.002997621308</v>
       </c>
       <c r="AE39">
-        <v>-0.0006508932757</v>
+        <v>-0.0006082719422</v>
       </c>
     </row>
     <row r="40" spans="1:31">
       <c r="A40">
-        <v>917.5455638</v>
+        <v>917.2248786</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4162,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>6.84238992117023</v>
+        <v>6.54062640417358</v>
       </c>
       <c r="E40">
         <v>94</v>
@@ -4174,13 +4162,13 @@
         <v>3</v>
       </c>
       <c r="H40">
-        <v>98.03850336000001</v>
+        <v>97.64139314000001</v>
       </c>
       <c r="I40">
-        <v>0.07626871440000001</v>
+        <v>0.3761380118</v>
       </c>
       <c r="J40">
-        <v>1.885227923</v>
+        <v>1.982468852</v>
       </c>
       <c r="K40">
         <v>94</v>
@@ -4237,18 +4225,18 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>0.002932197182</v>
+        <v>0.002767050749</v>
       </c>
       <c r="AD40">
-        <v>-0.002122964536</v>
+        <v>-0.001993987939</v>
       </c>
       <c r="AE40">
-        <v>-0.0008092326465</v>
+        <v>-0.0007730628101</v>
       </c>
     </row>
     <row r="41" spans="1:31">
       <c r="A41">
-        <v>910.2341158</v>
+        <v>909.6188072</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4257,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>10.317427561515</v>
+        <v>9.91991016742395</v>
       </c>
       <c r="E41">
         <v>93</v>
@@ -4269,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="H41">
-        <v>97.57817314</v>
+        <v>97.11122351</v>
       </c>
       <c r="I41">
-        <v>0.05547446248</v>
+        <v>0.411777038</v>
       </c>
       <c r="J41">
-        <v>2.366352393</v>
+        <v>2.476999452</v>
       </c>
       <c r="K41">
         <v>93</v>
@@ -4332,18 +4320,18 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0.002208202079</v>
+        <v>0.002063861127</v>
       </c>
       <c r="AD41">
-        <v>-0.001420343452</v>
+        <v>-0.00129938523</v>
       </c>
       <c r="AE41">
-        <v>-0.0007878586268</v>
+        <v>-0.0007644758966</v>
       </c>
     </row>
     <row r="42" spans="1:31">
       <c r="A42">
-        <v>900.8234935</v>
+        <v>899.9916392</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4352,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>15.0401391896126</v>
+        <v>14.3697982776203</v>
       </c>
       <c r="E42">
         <v>92</v>
@@ -4364,13 +4352,13 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>97.10134404999999</v>
+        <v>96.55326271</v>
       </c>
       <c r="I42">
-        <v>0.04169497664</v>
+        <v>0.4677916242</v>
       </c>
       <c r="J42">
-        <v>2.856960976</v>
+        <v>2.978945671</v>
       </c>
       <c r="K42">
         <v>92</v>
@@ -4427,13 +4415,13 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>0.00168989847</v>
+        <v>0.001579980893</v>
       </c>
       <c r="AD42">
-        <v>-0.0009800479329</v>
+        <v>-0.0008787175245</v>
       </c>
       <c r="AE42">
-        <v>-0.0007098505369</v>
+        <v>-0.0007012633684</v>
       </c>
     </row>
     <row r="43" spans="1:31">
@@ -4447,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>4.76276194554703</v>
+        <v>4.76068514532678</v>
       </c>
       <c r="E43">
         <v>96</v>
@@ -4530,7 +4518,7 @@
     </row>
     <row r="44" spans="1:31">
       <c r="A44">
-        <v>923.2286675</v>
+        <v>923.4759342999999</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -4539,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>4.97238596391683</v>
+        <v>4.62382115835657</v>
       </c>
       <c r="E44">
         <v>95</v>
@@ -4551,13 +4539,13 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>98.99772652</v>
+        <v>98.71026863</v>
       </c>
       <c r="I44">
-        <v>0.231322897</v>
+        <v>0.4512884312</v>
       </c>
       <c r="J44">
-        <v>0.7709505839</v>
+        <v>0.8384429363</v>
       </c>
       <c r="K44">
         <v>95</v>
@@ -4614,18 +4602,18 @@
         <v>0</v>
       </c>
       <c r="AC44">
-        <v>0.003987016154</v>
+        <v>0.003976927637</v>
       </c>
       <c r="AD44">
-        <v>-0.003758610828</v>
+        <v>-0.003803817636</v>
       </c>
       <c r="AE44">
-        <v>-0.0002284053261</v>
+        <v>-0.0001731100009</v>
       </c>
     </row>
     <row r="45" spans="1:31">
       <c r="A45">
-        <v>920.3776354</v>
+        <v>920.3250988</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -4634,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>5.93127829323508</v>
+        <v>5.54826509406006</v>
       </c>
       <c r="E45">
         <v>94</v>
@@ -4646,13 +4634,13 @@
         <v>2</v>
       </c>
       <c r="H45">
-        <v>98.50305317999999</v>
+        <v>98.06698432</v>
       </c>
       <c r="I45">
-        <v>0.1497124953</v>
+        <v>0.4803274142</v>
       </c>
       <c r="J45">
-        <v>1.347234328</v>
+        <v>1.452688263</v>
       </c>
       <c r="K45">
         <v>94</v>
@@ -4709,18 +4697,18 @@
         <v>0</v>
       </c>
       <c r="AC45">
-        <v>0.003768136489</v>
+        <v>0.003638797313</v>
       </c>
       <c r="AD45">
-        <v>-0.003222016488</v>
+        <v>-0.003149245617</v>
       </c>
       <c r="AE45">
-        <v>-0.0005461200007</v>
+        <v>-0.0004895516964</v>
       </c>
     </row>
     <row r="46" spans="1:31">
       <c r="A46">
-        <v>915.1945432</v>
+        <v>914.725207</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -4729,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>8.213546583436591</v>
+        <v>7.80539836083204</v>
       </c>
       <c r="E46">
         <v>93</v>
@@ -4741,13 +4729,13 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>98.04554387</v>
+        <v>97.5043034</v>
       </c>
       <c r="I46">
-        <v>0.1040526984</v>
+        <v>0.5150175625</v>
       </c>
       <c r="J46">
-        <v>1.850403433</v>
+        <v>1.980679042</v>
       </c>
       <c r="K46">
         <v>93</v>
@@ -4804,18 +4792,18 @@
         <v>0</v>
       </c>
       <c r="AC46">
-        <v>0.003053033287</v>
+        <v>0.002870374311</v>
       </c>
       <c r="AD46">
-        <v>-0.002357533753</v>
+        <v>-0.002220923212</v>
       </c>
       <c r="AE46">
-        <v>-0.0006954995333</v>
+        <v>-0.0006494510985</v>
       </c>
     </row>
     <row r="47" spans="1:31">
       <c r="A47">
-        <v>907.7811536</v>
+        <v>906.9420534</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4824,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>11.9440256047165</v>
+        <v>11.3338300351602</v>
       </c>
       <c r="E47">
         <v>92</v>
@@ -4836,13 +4824,13 @@
         <v>4</v>
       </c>
       <c r="H47">
-        <v>97.58548041</v>
+        <v>96.9422186</v>
       </c>
       <c r="I47">
-        <v>0.0759021616</v>
+        <v>0.5699112902</v>
       </c>
       <c r="J47">
-        <v>2.338617427</v>
+        <v>2.487870114</v>
       </c>
       <c r="K47">
         <v>92</v>
@@ -4899,18 +4887,18 @@
         <v>0</v>
       </c>
       <c r="AC47">
-        <v>0.002327368955</v>
+        <v>0.0021724365</v>
       </c>
       <c r="AD47">
-        <v>-0.001635185215</v>
+        <v>-0.00150782334</v>
       </c>
       <c r="AE47">
-        <v>-0.0006921837404</v>
+        <v>-0.00066461316</v>
       </c>
     </row>
     <row r="48" spans="1:31">
       <c r="A48">
-        <v>898.1326312</v>
+        <v>897.0359302000001</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -4919,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>17.0087658129</v>
+        <v>15.9268207343324</v>
       </c>
       <c r="E48">
         <v>91</v>
@@ -4931,13 +4919,13 @@
         <v>5</v>
       </c>
       <c r="H48">
-        <v>97.10309672</v>
+        <v>96.3401437</v>
       </c>
       <c r="I48">
-        <v>0.05712184422</v>
+        <v>0.6546093949</v>
       </c>
       <c r="J48">
-        <v>2.83978144</v>
+        <v>3.005246903</v>
       </c>
       <c r="K48">
         <v>91</v>
@@ -4994,13 +4982,13 @@
         <v>0</v>
       </c>
       <c r="AC48">
-        <v>0.001788779541</v>
+        <v>0.001672319277</v>
       </c>
       <c r="AD48">
-        <v>-0.001155689995</v>
+        <v>-0.001047681349</v>
       </c>
       <c r="AE48">
-        <v>-0.0006330895465</v>
+        <v>-0.0006246379281</v>
       </c>
     </row>
     <row r="49" spans="1:31">
@@ -5014,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1.14741811542448</v>
+        <v>1.14585303240547</v>
       </c>
       <c r="E49">
         <v>98</v>
@@ -5106,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>6.00585498101498</v>
+        <v>6.0063165804869</v>
       </c>
       <c r="E50">
         <v>95</v>
@@ -5189,7 +5177,7 @@
     </row>
     <row r="51" spans="1:31">
       <c r="A51">
-        <v>920.6550126</v>
+        <v>920.9056563</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -5198,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>6.20564389749978</v>
+        <v>5.82740529141029</v>
       </c>
       <c r="E51">
         <v>94</v>
@@ -5210,13 +5198,13 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>98.96290505</v>
+        <v>98.60289788</v>
       </c>
       <c r="I51">
-        <v>0.2929196791</v>
+        <v>0.5695498479</v>
       </c>
       <c r="J51">
-        <v>0.7441752686000001</v>
+        <v>0.8275522722</v>
       </c>
       <c r="K51">
         <v>94</v>
@@ -5273,18 +5261,18 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>0.003970382745</v>
+        <v>0.00392137879</v>
       </c>
       <c r="AD51">
-        <v>-0.003765734308</v>
+        <v>-0.003774500332</v>
       </c>
       <c r="AE51">
-        <v>-0.0002046484368</v>
+        <v>-0.0001468784579</v>
       </c>
     </row>
     <row r="52" spans="1:31">
       <c r="A52">
-        <v>917.9442326</v>
+        <v>917.8132345</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5293,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>7.21409748519385</v>
+        <v>6.77893369537961</v>
       </c>
       <c r="E52">
         <v>93</v>
@@ -5305,13 +5293,13 @@
         <v>2</v>
       </c>
       <c r="H52">
-        <v>98.49700924</v>
+        <v>97.94489989</v>
       </c>
       <c r="I52">
-        <v>0.1906963392</v>
+        <v>0.6112982442</v>
       </c>
       <c r="J52">
-        <v>1.312294417</v>
+        <v>1.443801867</v>
       </c>
       <c r="K52">
         <v>93</v>
@@ -5368,18 +5356,18 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>0.003784377849</v>
+        <v>0.003625071664</v>
       </c>
       <c r="AD52">
-        <v>-0.003311003921</v>
+        <v>-0.003217421775</v>
       </c>
       <c r="AE52">
-        <v>-0.0004733739281</v>
+        <v>-0.0004076498884</v>
       </c>
     </row>
     <row r="53" spans="1:31">
       <c r="A53">
-        <v>912.7760235</v>
+        <v>912.1411336</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -5388,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>9.679595378109671</v>
+        <v>9.14665748184829</v>
       </c>
       <c r="E53">
         <v>92</v>
@@ -5400,13 +5388,13 @@
         <v>3</v>
       </c>
       <c r="H53">
-        <v>98.04985252</v>
+        <v>97.35687367</v>
       </c>
       <c r="I53">
-        <v>0.1331281314</v>
+        <v>0.6622980197</v>
       </c>
       <c r="J53">
-        <v>1.817019351</v>
+        <v>1.980828315</v>
       </c>
       <c r="K53">
         <v>92</v>
@@ -5463,18 +5451,18 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>0.003107021056</v>
+        <v>0.002914905053</v>
       </c>
       <c r="AD53">
-        <v>-0.002499563534</v>
+        <v>-0.002360417996</v>
       </c>
       <c r="AE53">
-        <v>-0.0006074575227</v>
+        <v>-0.0005544870577</v>
       </c>
     </row>
     <row r="54" spans="1:31">
       <c r="A54">
-        <v>905.2247869</v>
+        <v>904.1583963</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -5483,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>13.7130392555078</v>
+        <v>12.8263996093165</v>
       </c>
       <c r="E54">
         <v>91</v>
@@ -5495,13 +5483,13 @@
         <v>4</v>
       </c>
       <c r="H54">
-        <v>97.59024316999999</v>
+        <v>96.75750863</v>
       </c>
       <c r="I54">
-        <v>0.09738475874999999</v>
+        <v>0.7411350922</v>
       </c>
       <c r="J54">
-        <v>2.312372069</v>
+        <v>2.501356275</v>
       </c>
       <c r="K54">
         <v>91</v>
@@ -5558,18 +5546,18 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>0.002391840238</v>
+        <v>0.002237137389</v>
       </c>
       <c r="AD54">
-        <v>-0.001779406877</v>
+        <v>-0.001654883579</v>
       </c>
       <c r="AE54">
-        <v>-0.0006124333611</v>
+        <v>-0.0005822538093</v>
       </c>
     </row>
     <row r="55" spans="1:31">
       <c r="A55">
-        <v>895.3041972</v>
+        <v>893.9578129</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -5578,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>19.148842636162</v>
+        <v>17.5399982902861</v>
       </c>
       <c r="E55">
         <v>90</v>
@@ -5590,13 +5578,13 @@
         <v>5</v>
       </c>
       <c r="H55">
-        <v>97.10239785</v>
+        <v>96.10400260999999</v>
       </c>
       <c r="I55">
-        <v>0.07337368545</v>
+        <v>0.8610803157</v>
       </c>
       <c r="J55">
-        <v>2.824228467</v>
+        <v>3.034917076</v>
       </c>
       <c r="K55">
         <v>90</v>
@@ -5653,13 +5641,13 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0.001848871303</v>
+        <v>0.001736147656</v>
       </c>
       <c r="AD55">
-        <v>-0.001282531566</v>
+        <v>-0.001177258583</v>
       </c>
       <c r="AE55">
-        <v>-0.0005663397372</v>
+        <v>-0.0005588890727</v>
       </c>
     </row>
     <row r="56" spans="1:31">
@@ -5673,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>7.27189695074592</v>
+        <v>7.27560961998251</v>
       </c>
       <c r="E56">
         <v>94</v>
@@ -5756,7 +5744,7 @@
     </row>
     <row r="57" spans="1:31">
       <c r="A57">
-        <v>918.0648831</v>
+        <v>918.2977623</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -5765,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>7.46000988609314</v>
+        <v>7.06937736360042</v>
       </c>
       <c r="E57">
         <v>93</v>
@@ -5777,13 +5765,13 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>98.92529485999999</v>
+        <v>98.49183651</v>
       </c>
       <c r="I57">
-        <v>0.3562248092</v>
+        <v>0.6907276277</v>
       </c>
       <c r="J57">
-        <v>0.7184803258</v>
+        <v>0.8174358615</v>
       </c>
       <c r="K57">
         <v>93</v>
@@ -5840,18 +5828,18 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0.003945760278</v>
+        <v>0.003861148115</v>
       </c>
       <c r="AD57">
-        <v>-0.003758297804</v>
+        <v>-0.003732817211</v>
       </c>
       <c r="AE57">
-        <v>-0.0001874624741</v>
+        <v>-0.0001283309041</v>
       </c>
     </row>
     <row r="58" spans="1:31">
       <c r="A58">
-        <v>915.470519</v>
+        <v>915.2384393</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -5860,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>8.55403361128068</v>
+        <v>8.072052838943099</v>
       </c>
       <c r="E58">
         <v>92</v>
@@ -5872,13 +5860,13 @@
         <v>2</v>
       </c>
       <c r="H58">
-        <v>98.48801090000001</v>
+        <v>97.81573554000001</v>
       </c>
       <c r="I58">
-        <v>0.2332715982</v>
+        <v>0.7479527215</v>
       </c>
       <c r="J58">
-        <v>1.2787175</v>
+        <v>1.436311735</v>
       </c>
       <c r="K58">
         <v>92</v>
@@ -5935,18 +5923,18 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>0.003768322469</v>
+        <v>0.003583418644</v>
       </c>
       <c r="AD58">
-        <v>-0.003349441048</v>
+        <v>-0.003236166481</v>
       </c>
       <c r="AE58">
-        <v>-0.0004188814208</v>
+        <v>-0.0003472521622</v>
       </c>
     </row>
     <row r="59" spans="1:31">
       <c r="A59">
-        <v>910.2825594</v>
+        <v>909.4679134</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -5955,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>11.2535175449065</v>
+        <v>10.5665925115384</v>
       </c>
       <c r="E59">
         <v>91</v>
@@ -5967,13 +5955,13 @@
         <v>3</v>
       </c>
       <c r="H59">
-        <v>98.05137498000001</v>
+        <v>97.19776349</v>
       </c>
       <c r="I59">
-        <v>0.1635692672</v>
+        <v>0.8192072787</v>
       </c>
       <c r="J59">
-        <v>1.785055754</v>
+        <v>1.98302923</v>
       </c>
       <c r="K59">
         <v>91</v>
@@ -6030,13 +6018,13 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0.003115273409</v>
+        <v>0.002920771508</v>
       </c>
       <c r="AD59">
-        <v>-0.002578579721</v>
+        <v>-0.002441581804</v>
       </c>
       <c r="AE59">
-        <v>-0.0005366936874</v>
+        <v>-0.0004791897042</v>
       </c>
     </row>
     <row r="60" spans="1:31">
@@ -6050,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>3.16169842283276</v>
+        <v>3.17111200947613</v>
       </c>
       <c r="E60">
         <v>97</v>
@@ -6133,7 +6121,7 @@
     </row>
     <row r="61" spans="1:31">
       <c r="A61">
-        <v>902.5569966</v>
+        <v>901.2640005</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -6142,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>15.6464362446977</v>
+        <v>14.3933630788912</v>
       </c>
       <c r="E61">
         <v>90</v>
@@ -6154,13 +6142,13 @@
         <v>4</v>
       </c>
       <c r="H61">
-        <v>97.59240586999999</v>
+        <v>96.55487960000001</v>
       </c>
       <c r="I61">
-        <v>0.1199791107</v>
+        <v>0.9274768490999999</v>
       </c>
       <c r="J61">
-        <v>2.287615017</v>
+        <v>2.517643552</v>
       </c>
       <c r="K61">
         <v>90</v>
@@ -6217,18 +6205,18 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0.002416340258</v>
+        <v>0.002270429496</v>
       </c>
       <c r="AD61">
-        <v>-0.001871416517</v>
+        <v>-0.001757032605</v>
       </c>
       <c r="AE61">
-        <v>-0.0005449237407</v>
+        <v>-0.0005133968906000001</v>
       </c>
     </row>
     <row r="62" spans="1:31">
       <c r="A62">
-        <v>892.3297636999999</v>
+        <v>890.7555134</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -6237,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>21.4823670360539</v>
+        <v>19.1947272951834</v>
       </c>
       <c r="E62">
         <v>89</v>
@@ -6249,13 +6237,13 @@
         <v>5</v>
       </c>
       <c r="H62">
-        <v>97.09918492</v>
+        <v>95.84129672</v>
       </c>
       <c r="I62">
-        <v>0.09048882693</v>
+        <v>1.090491479</v>
       </c>
       <c r="J62">
-        <v>2.810326253</v>
+        <v>3.068211797</v>
       </c>
       <c r="K62">
         <v>89</v>
@@ -6312,13 +6300,13 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>0.001879081287</v>
+        <v>0.001778514768</v>
       </c>
       <c r="AD62">
-        <v>-0.00137110032</v>
+        <v>-0.001276343812</v>
       </c>
       <c r="AE62">
-        <v>-0.0005079809669</v>
+        <v>-0.0005021709561</v>
       </c>
     </row>
     <row r="63" spans="1:31">
@@ -6332,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>8.564119972817689</v>
+        <v>8.57182889292617</v>
       </c>
       <c r="E63">
         <v>93</v>
@@ -6415,7 +6403,7 @@
     </row>
     <row r="64" spans="1:31">
       <c r="A64">
-        <v>915.4530741</v>
+        <v>915.6481906</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -6424,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>8.74408192545234</v>
+        <v>8.355265025343771</v>
       </c>
       <c r="E64">
         <v>92</v>
@@ -6436,13 +6424,13 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>98.88480868000001</v>
+        <v>98.37662841</v>
       </c>
       <c r="I64">
-        <v>0.4213580138</v>
+        <v>0.8152611224</v>
       </c>
       <c r="J64">
-        <v>0.6938333017</v>
+        <v>0.8081104702</v>
       </c>
       <c r="K64">
         <v>92</v>
@@ -6499,18 +6487,18 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>0.00391288743</v>
+        <v>0.003796369062</v>
       </c>
       <c r="AD64">
-        <v>-0.003738884182</v>
+        <v>-0.003682144207</v>
       </c>
       <c r="AE64">
-        <v>-0.0001740032487</v>
+        <v>-0.0001142248553</v>
       </c>
     </row>
     <row r="65" spans="1:31">
       <c r="A65">
-        <v>912.9497445</v>
+        <v>912.5958759</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -6519,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>9.96337944718336</v>
+        <v>9.43254459202454</v>
       </c>
       <c r="E65">
         <v>91</v>
@@ -6531,13 +6519,13 @@
         <v>2</v>
       </c>
       <c r="H65">
-        <v>98.47599129</v>
+        <v>97.67860580999999</v>
       </c>
       <c r="I65">
-        <v>0.2775365033</v>
+        <v>0.891115152</v>
       </c>
       <c r="J65">
-        <v>1.246472209</v>
+        <v>1.430279035</v>
       </c>
       <c r="K65">
         <v>91</v>
@@ -6594,18 +6582,18 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>0.003728700771</v>
+        <v>0.003523784772</v>
       </c>
       <c r="AD65">
-        <v>-0.003352908188</v>
+        <v>-0.00322324003</v>
       </c>
       <c r="AE65">
-        <v>-0.000375792583</v>
+        <v>-0.0003005447421</v>
       </c>
     </row>
     <row r="66" spans="1:31">
       <c r="A66">
-        <v>907.7064956</v>
+        <v>906.7008642</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -6614,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>12.9485525302076</v>
+        <v>12.0662039939907</v>
       </c>
       <c r="E66">
         <v>90</v>
@@ -6626,13 +6614,13 @@
         <v>3</v>
       </c>
       <c r="H66">
-        <v>98.05005047</v>
+        <v>97.02540904</v>
       </c>
       <c r="I66">
-        <v>0.195456105</v>
+        <v>0.9871800509000001</v>
       </c>
       <c r="J66">
-        <v>1.754493424</v>
+        <v>1.98741091</v>
       </c>
       <c r="K66">
         <v>90</v>
@@ -6689,18 +6677,18 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>0.003090983885</v>
+        <v>0.002900589649</v>
       </c>
       <c r="AD66">
-        <v>-0.002612795396</v>
+        <v>-0.002482577739</v>
       </c>
       <c r="AE66">
-        <v>-0.000478188489</v>
+        <v>-0.0004180119096</v>
       </c>
     </row>
     <row r="67" spans="1:31">
       <c r="A67">
-        <v>899.769536</v>
+        <v>898.2553927</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -6709,7 +6697,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>17.7414756163009</v>
+        <v>16.0278189159211</v>
       </c>
       <c r="E67">
         <v>89</v>
@@ -6721,13 +6709,13 @@
         <v>4</v>
       </c>
       <c r="H67">
-        <v>97.59190733</v>
+        <v>96.33170448</v>
       </c>
       <c r="I67">
-        <v>0.1437455171</v>
+        <v>1.13135303</v>
       </c>
       <c r="J67">
-        <v>2.264347156</v>
+        <v>2.536942486</v>
       </c>
       <c r="K67">
         <v>89</v>
@@ -6784,18 +6772,18 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>0.002411375725</v>
+        <v>0.002281206684</v>
       </c>
       <c r="AD67">
-        <v>-0.001924298714</v>
+        <v>-0.001826030295</v>
       </c>
       <c r="AE67">
-        <v>-0.0004870770112</v>
+        <v>-0.0004551763896</v>
       </c>
     </row>
     <row r="68" spans="1:31">
       <c r="A68">
-        <v>889.2006618</v>
+        <v>887.4281457</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -6804,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>24.02209906198</v>
+        <v>20.8715755660548</v>
       </c>
       <c r="E68">
         <v>88</v>
@@ -6816,13 +6804,13 @@
         <v>5</v>
       </c>
       <c r="H68">
-        <v>97.09339009</v>
+        <v>95.54777419</v>
       </c>
       <c r="I68">
-        <v>0.1085067549</v>
+        <v>1.3468119</v>
       </c>
       <c r="J68">
-        <v>2.798103158</v>
+        <v>3.105413907</v>
       </c>
       <c r="K68">
         <v>88</v>
@@ -6879,13 +6867,13 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>0.00188637531</v>
+        <v>0.001804924628</v>
       </c>
       <c r="AD68">
-        <v>-0.001429639759</v>
+        <v>-0.001351893566</v>
       </c>
       <c r="AE68">
-        <v>-0.0004567355511</v>
+        <v>-0.0004530310625</v>
       </c>
     </row>
     <row r="69" spans="1:31">
@@ -6899,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>9.88603636981995</v>
+        <v>9.8985202189711</v>
       </c>
       <c r="E69">
         <v>92</v>
@@ -6982,7 +6970,7 @@
     </row>
     <row r="70" spans="1:31">
       <c r="A70">
-        <v>912.814196</v>
+        <v>912.9527161</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -6991,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>10.0666920148375</v>
+        <v>9.69070991808178</v>
       </c>
       <c r="E70">
         <v>91</v>
@@ -7003,13 +6991,13 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>98.84134693</v>
+        <v>98.25676442</v>
       </c>
       <c r="I70">
-        <v>0.4884513325</v>
+        <v>0.9436396533</v>
       </c>
       <c r="J70">
-        <v>0.6702017327999999</v>
+        <v>0.7995959308</v>
       </c>
       <c r="K70">
         <v>91</v>
@@ -7066,13 +7054,13 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>0.003871704405</v>
+        <v>0.003727302407</v>
       </c>
       <c r="AD70">
-        <v>-0.003708865011</v>
+        <v>-0.00362438237</v>
       </c>
       <c r="AE70">
-        <v>-0.0001628393948</v>
+        <v>-0.0001029200365</v>
       </c>
     </row>
     <row r="71" spans="1:31">
@@ -7086,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>5.75639008875046</v>
+        <v>6.1633020042692</v>
       </c>
       <c r="E71">
         <v>96</v>
@@ -7169,7 +7157,7 @@
     </row>
     <row r="72" spans="1:31">
       <c r="A72">
-        <v>910.3749586</v>
+        <v>909.8806273</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -7178,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>11.4541680384741</v>
+        <v>10.8649707505658</v>
       </c>
       <c r="E72">
         <v>90</v>
@@ -7190,13 +7178,13 @@
         <v>2</v>
       </c>
       <c r="H72">
-        <v>98.46087455</v>
+        <v>97.53249423</v>
       </c>
       <c r="I72">
-        <v>0.3235982638</v>
+        <v>1.041731114</v>
       </c>
       <c r="J72">
-        <v>1.215527185</v>
+        <v>1.425774651</v>
       </c>
       <c r="K72">
         <v>90</v>
@@ -7253,18 +7241,18 @@
         <v>0</v>
       </c>
       <c r="AC72">
-        <v>0.003670938202</v>
+        <v>0.003452105399</v>
       </c>
       <c r="AD72">
-        <v>-0.003330602242</v>
+        <v>-0.003188982639</v>
       </c>
       <c r="AE72">
-        <v>-0.0003403359597</v>
+        <v>-0.0002631227599</v>
       </c>
     </row>
     <row r="73" spans="1:31">
       <c r="A73">
-        <v>905.0399585</v>
+        <v>903.8354178</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -7273,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>14.7782079984753</v>
+        <v>13.6449622200305</v>
       </c>
       <c r="E73">
         <v>89</v>
@@ -7285,13 +7273,13 @@
         <v>3</v>
       </c>
       <c r="H73">
-        <v>98.04581109</v>
+        <v>96.83797318000001</v>
       </c>
       <c r="I73">
-        <v>0.2288748827</v>
+        <v>1.167905015</v>
       </c>
       <c r="J73">
-        <v>1.725314029</v>
+        <v>1.994121804</v>
       </c>
       <c r="K73">
         <v>89</v>
@@ -7348,18 +7336,18 @@
         <v>0</v>
       </c>
       <c r="AC73">
-        <v>0.003043158618</v>
+        <v>0.002862720636</v>
       </c>
       <c r="AD73">
-        <v>-0.002614372202</v>
+        <v>-0.002495383672</v>
       </c>
       <c r="AE73">
-        <v>-0.0004287864164</v>
+        <v>-0.0003673369643</v>
       </c>
     </row>
     <row r="74" spans="1:31">
       <c r="A74">
-        <v>896.8539207</v>
+        <v>895.1295848</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -7368,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>20.0176211965992</v>
+        <v>17.7195621942884</v>
       </c>
       <c r="E74">
         <v>88</v>
@@ -7380,13 +7368,13 @@
         <v>4</v>
       </c>
       <c r="H74">
-        <v>97.58868029999999</v>
+        <v>96.08484478</v>
       </c>
       <c r="I74">
-        <v>0.1687479064</v>
+        <v>1.355663186</v>
       </c>
       <c r="J74">
-        <v>2.242571796</v>
+        <v>2.559492037</v>
       </c>
       <c r="K74">
         <v>88</v>
@@ -7443,18 +7431,18 @@
         <v>0</v>
       </c>
       <c r="AC74">
-        <v>0.002384698363</v>
+        <v>0.00227599032</v>
       </c>
       <c r="AD74">
-        <v>-0.001947664449</v>
+        <v>-0.00187050591</v>
       </c>
       <c r="AE74">
-        <v>-0.000437033914</v>
+        <v>-0.0004054844099</v>
       </c>
     </row>
     <row r="75" spans="1:31">
       <c r="A75">
-        <v>885.9079723999999</v>
+        <v>883.9759642</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -7463,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>26.7810150370277</v>
+        <v>22.5444869567602</v>
       </c>
       <c r="E75">
         <v>87</v>
@@ -7475,13 +7463,13 @@
         <v>5</v>
       </c>
       <c r="H75">
-        <v>97.08493987999999</v>
+        <v>95.21830318000001</v>
       </c>
       <c r="I75">
-        <v>0.1274679898</v>
+        <v>1.634862607</v>
       </c>
       <c r="J75">
-        <v>2.787592129</v>
+        <v>3.146834212</v>
       </c>
       <c r="K75">
         <v>87</v>
@@ -7538,13 +7526,13 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>0.001876151969</v>
+        <v>0.001819765432</v>
       </c>
       <c r="AD75">
-        <v>-0.001464597587</v>
+        <v>-0.001409446443</v>
       </c>
       <c r="AE75">
-        <v>-0.0004115543815</v>
+        <v>-0.0004103189888</v>
       </c>
     </row>
     <row r="76" spans="1:31">
@@ -7558,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>11.2414363017552</v>
+        <v>11.2595326693337</v>
       </c>
       <c r="E76">
         <v>91</v>
@@ -7641,7 +7629,7 @@
     </row>
     <row r="77" spans="1:31">
       <c r="A77">
-        <v>910.1426675</v>
+        <v>910.2069494</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -7650,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>11.4374631884931</v>
+        <v>11.081423827909</v>
       </c>
       <c r="E77">
         <v>90</v>
@@ -7662,13 +7650,13 @@
         <v>1</v>
       </c>
       <c r="H77">
-        <v>98.79479634</v>
+        <v>98.13167314</v>
       </c>
       <c r="I77">
-        <v>0.5576503313</v>
+        <v>1.07641121</v>
       </c>
       <c r="J77">
-        <v>0.6475533253</v>
+        <v>0.7919156511</v>
       </c>
       <c r="K77">
         <v>90</v>
@@ -7725,18 +7713,18 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>0.003822329579</v>
+        <v>0.003654286575</v>
       </c>
       <c r="AD77">
-        <v>-0.003669150779</v>
+        <v>-0.003560786846</v>
       </c>
       <c r="AE77">
-        <v>-0.0001531787997</v>
+        <v>-9.349972939E-05</v>
       </c>
     </row>
     <row r="78" spans="1:31">
       <c r="A78">
-        <v>907.7390028</v>
+        <v>907.0877172</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -7745,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>13.0390767161903</v>
+        <v>12.3732524957398</v>
       </c>
       <c r="E78">
         <v>89</v>
@@ -7757,13 +7745,13 @@
         <v>2</v>
       </c>
       <c r="H78">
-        <v>98.44257483</v>
+        <v>97.37622598999999</v>
       </c>
       <c r="I78">
-        <v>0.3715739328</v>
+        <v>1.20089313</v>
       </c>
       <c r="J78">
-        <v>1.185851233</v>
+        <v>1.422880882</v>
       </c>
       <c r="K78">
         <v>89</v>
@@ -7820,18 +7808,18 @@
         <v>0</v>
       </c>
       <c r="AC78">
-        <v>0.003598809163</v>
+        <v>0.003372262937</v>
       </c>
       <c r="AD78">
-        <v>-0.003288534619</v>
+        <v>-0.003139949316</v>
       </c>
       <c r="AE78">
-        <v>-0.0003102745441</v>
+        <v>-0.0002323136214</v>
       </c>
     </row>
     <row r="79" spans="1:31">
       <c r="A79">
-        <v>902.2748473</v>
+        <v>900.8671861</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -7840,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>16.7649166982337</v>
+        <v>15.3003846145611</v>
       </c>
       <c r="E79">
         <v>88</v>
@@ -7852,13 +7840,13 @@
         <v>3</v>
       </c>
       <c r="H79">
-        <v>98.03858106</v>
+        <v>96.63328177</v>
       </c>
       <c r="I79">
-        <v>0.2639186241</v>
+        <v>1.363385226</v>
       </c>
       <c r="J79">
-        <v>1.697500314</v>
+        <v>2.003333005</v>
       </c>
       <c r="K79">
         <v>88</v>
@@ -7915,18 +7903,18 @@
         <v>0</v>
       </c>
       <c r="AC79">
-        <v>0.002978149826</v>
+        <v>0.002812961741</v>
       </c>
       <c r="AD79">
-        <v>-0.002591767505</v>
+        <v>-0.002488260086</v>
       </c>
       <c r="AE79">
-        <v>-0.0003863823215</v>
+        <v>-0.0003247016551</v>
       </c>
     </row>
     <row r="80" spans="1:31">
       <c r="A80">
-        <v>893.8014202000001</v>
+        <v>891.8842316</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -7935,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>22.4906764621538</v>
+        <v>19.4542312383236</v>
       </c>
       <c r="E80">
         <v>87</v>
@@ -7947,13 +7935,13 @@
         <v>4</v>
       </c>
       <c r="H80">
-        <v>97.58265093999999</v>
+        <v>95.81052394</v>
       </c>
       <c r="I80">
-        <v>0.1950540385</v>
+        <v>1.603912634</v>
       </c>
       <c r="J80">
-        <v>2.222295019</v>
+        <v>2.585563425</v>
       </c>
       <c r="K80">
         <v>87</v>
@@ -8010,18 +7998,18 @@
         <v>0</v>
       </c>
       <c r="AC80">
-        <v>0.00234203533</v>
+        <v>0.002259688416</v>
       </c>
       <c r="AD80">
-        <v>-0.001948644175</v>
+        <v>-0.001896952198</v>
       </c>
       <c r="AE80">
-        <v>-0.0003933911551</v>
+        <v>-0.0003627362175</v>
       </c>
     </row>
     <row r="81" spans="1:31">
       <c r="A81">
-        <v>882.4425177000001</v>
+        <v>880.4006851</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -8030,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>29.7722848201984</v>
+        <v>24.1835022942322</v>
       </c>
       <c r="E81">
         <v>86</v>
@@ -8042,13 +8030,13 @@
         <v>5</v>
       </c>
       <c r="H81">
-        <v>97.07375491000001</v>
+        <v>94.84665685</v>
       </c>
       <c r="I81">
-        <v>0.1474139152</v>
+        <v>1.960532615</v>
       </c>
       <c r="J81">
-        <v>2.778831176</v>
+        <v>3.192810531</v>
       </c>
       <c r="K81">
         <v>86</v>
@@ -8105,13 +8093,13 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0.001852650848</v>
+        <v>0.001826585872</v>
       </c>
       <c r="AD81">
-        <v>-0.00148107349</v>
+        <v>-0.001453473797</v>
       </c>
       <c r="AE81">
-        <v>-0.0003715773587</v>
+        <v>-0.0003731120752</v>
       </c>
     </row>
     <row r="82" spans="1:31">
@@ -8125,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>8.590007519816499</v>
+        <v>10.1278164272784</v>
       </c>
       <c r="E82">
         <v>95</v>
@@ -8217,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>12.6344169005572</v>
+        <v>12.659019737941</v>
       </c>
       <c r="E83">
         <v>90</v>
@@ -8300,7 +8288,7 @@
     </row>
     <row r="84" spans="1:31">
       <c r="A84">
-        <v>907.4327086</v>
+        <v>907.4063374999999</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -8309,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>12.8657040953004</v>
+        <v>12.5331353554759</v>
       </c>
       <c r="E84">
         <v>89</v>
@@ -8321,13 +8309,13 @@
         <v>1</v>
       </c>
       <c r="H84">
-        <v>98.74502851</v>
+        <v>98.00070968999999</v>
       </c>
       <c r="I84">
-        <v>0.6291154802</v>
+        <v>1.214193092</v>
       </c>
       <c r="J84">
-        <v>0.6258560053</v>
+        <v>0.7850972208</v>
       </c>
       <c r="K84">
         <v>89</v>
@@ -8384,18 +8372,18 @@
         <v>0</v>
       </c>
       <c r="AC84">
-        <v>0.003765069965</v>
+        <v>0.003577713405</v>
       </c>
       <c r="AD84">
-        <v>-0.003620514713</v>
+        <v>-0.003492300564</v>
       </c>
       <c r="AE84">
-        <v>-0.000144555252</v>
+        <v>-8.541284151E-05</v>
       </c>
     </row>
     <row r="85" spans="1:31">
       <c r="A85">
-        <v>905.0345035</v>
+        <v>904.2121357</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -8404,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>14.7309832002343</v>
+        <v>13.9604728262703</v>
       </c>
       <c r="E85">
         <v>88</v>
@@ -8416,13 +8404,13 @@
         <v>2</v>
       </c>
       <c r="H85">
-        <v>98.42099512999999</v>
+        <v>97.2084334</v>
       </c>
       <c r="I85">
-        <v>0.4215913859</v>
+        <v>1.369873108</v>
       </c>
       <c r="J85">
-        <v>1.157413481</v>
+        <v>1.421693492</v>
       </c>
       <c r="K85">
         <v>88</v>
@@ -8479,18 +8467,18 @@
         <v>0</v>
       </c>
       <c r="AC85">
-        <v>0.003515210388</v>
+        <v>0.003286985676</v>
       </c>
       <c r="AD85">
-        <v>-0.003231003199</v>
+        <v>-0.003080585497</v>
       </c>
       <c r="AE85">
-        <v>-0.0002842071888</v>
+        <v>-0.000206400179</v>
       </c>
     </row>
     <row r="86" spans="1:31">
       <c r="A86">
-        <v>899.4028245</v>
+        <v>897.7920456000001</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -8499,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>18.9064352225662</v>
+        <v>17.0274935205087</v>
       </c>
       <c r="E86">
         <v>87</v>
@@ -8511,13 +8499,13 @@
         <v>3</v>
       </c>
       <c r="H86">
-        <v>98.02827597</v>
+        <v>96.4087415</v>
       </c>
       <c r="I86">
-        <v>0.3006877488</v>
+        <v>1.576016254</v>
       </c>
       <c r="J86">
-        <v>1.671036286</v>
+        <v>2.01524225</v>
       </c>
       <c r="K86">
         <v>87</v>
@@ -8574,18 +8562,18 @@
         <v>0</v>
       </c>
       <c r="AC86">
-        <v>0.002900682483</v>
+        <v>0.002755489876</v>
       </c>
       <c r="AD86">
-        <v>-0.002551160136</v>
+        <v>-0.002467123291</v>
       </c>
       <c r="AE86">
-        <v>-0.0003495223472</v>
+        <v>-0.0002883665845</v>
       </c>
     </row>
     <row r="87" spans="1:31">
       <c r="A87">
-        <v>890.6030469999999</v>
+        <v>888.5178341</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -8594,7 +8582,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>25.1740134205136</v>
+        <v>21.2121805814158</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -8606,13 +8594,13 @@
         <v>4</v>
       </c>
       <c r="H87">
-        <v>97.57373839</v>
+        <v>95.504164</v>
       </c>
       <c r="I87">
-        <v>0.2227356936</v>
+        <v>1.880371831</v>
       </c>
       <c r="J87">
-        <v>2.203525921</v>
+        <v>2.615464174</v>
       </c>
       <c r="K87">
         <v>86</v>
@@ -8669,18 +8657,18 @@
         <v>0</v>
       </c>
       <c r="AC87">
-        <v>0.002287785994</v>
+        <v>0.0022360989</v>
       </c>
       <c r="AD87">
-        <v>-0.001932701878</v>
+        <v>-0.001910380365</v>
       </c>
       <c r="AE87">
-        <v>-0.0003550841151</v>
+        <v>-0.0003257185348</v>
       </c>
     </row>
     <row r="88" spans="1:31">
       <c r="A88">
-        <v>878.794852</v>
+        <v>876.7058962</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -8689,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>33.0092513610776</v>
+        <v>25.7456135754132</v>
       </c>
       <c r="E88">
         <v>85</v>
@@ -8701,13 +8689,13 @@
         <v>5</v>
       </c>
       <c r="H88">
-        <v>97.05974955000001</v>
+        <v>94.42524537</v>
       </c>
       <c r="I88">
-        <v>0.1683865499</v>
+        <v>2.331051377</v>
       </c>
       <c r="J88">
-        <v>2.771863899</v>
+        <v>3.243703249</v>
       </c>
       <c r="K88">
         <v>85</v>
@@ -8764,13 +8752,13 @@
         <v>0</v>
       </c>
       <c r="AC88">
-        <v>0.001819208308</v>
+        <v>0.001828409155</v>
       </c>
       <c r="AD88">
-        <v>-0.001483117653</v>
+        <v>-0.001487723314</v>
       </c>
       <c r="AE88">
-        <v>-0.0003360906549</v>
+        <v>-0.0003406858412</v>
       </c>
     </row>
     <row r="89" spans="1:31">
@@ -8784,7 +8772,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>14.069387199957</v>
+        <v>14.1014608667143</v>
       </c>
       <c r="E89">
         <v>89</v>
@@ -8867,7 +8855,7 @@
     </row>
     <row r="90" spans="1:31">
       <c r="A90">
-        <v>904.6783329</v>
+        <v>904.5461663</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -8876,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>14.3615121968059</v>
+        <v>14.0515170419474</v>
       </c>
       <c r="E90">
         <v>88</v>
@@ -8888,13 +8876,13 @@
         <v>1</v>
       </c>
       <c r="H90">
-        <v>98.69189821000001</v>
+        <v>97.86314183</v>
       </c>
       <c r="I90">
-        <v>0.7030237566</v>
+        <v>1.357685032</v>
       </c>
       <c r="J90">
-        <v>0.6050780368000001</v>
+        <v>0.7791731382</v>
       </c>
       <c r="K90">
         <v>88</v>
@@ -8951,18 +8939,18 @@
         <v>0</v>
       </c>
       <c r="AC90">
-        <v>0.003700328615</v>
+        <v>0.003498013643</v>
       </c>
       <c r="AD90">
-        <v>-0.003563649203</v>
+        <v>-0.00341970439</v>
       </c>
       <c r="AE90">
-        <v>-0.0001366794115</v>
+        <v>-7.830925387E-05</v>
       </c>
     </row>
     <row r="91" spans="1:31">
       <c r="A91">
-        <v>902.2538627</v>
+        <v>901.248873</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -8971,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>16.5509483646341</v>
+        <v>15.6286007865356</v>
       </c>
       <c r="E91">
         <v>87</v>
@@ -8983,13 +8971,13 @@
         <v>2</v>
       </c>
       <c r="H91">
-        <v>98.39602601999999</v>
+        <v>97.02751191999999</v>
       </c>
       <c r="I91">
-        <v>0.4737904468</v>
+        <v>1.550163838</v>
       </c>
       <c r="J91">
-        <v>1.130183532</v>
+        <v>1.422324242</v>
       </c>
       <c r="K91">
         <v>87</v>
@@ -9046,18 +9034,18 @@
         <v>0</v>
       </c>
       <c r="AC91">
-        <v>0.003422509162</v>
+        <v>0.003198304384</v>
       </c>
       <c r="AD91">
-        <v>-0.00316129266</v>
+        <v>-0.003014077428</v>
       </c>
       <c r="AE91">
-        <v>-0.0002612165022</v>
+        <v>-0.000184226956</v>
       </c>
     </row>
     <row r="92" spans="1:31">
       <c r="A92">
-        <v>896.4153058000001</v>
+        <v>894.6062470000001</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -9066,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>21.2247578302994</v>
+        <v>18.818125888146</v>
       </c>
       <c r="E92">
         <v>86</v>
@@ -9078,13 +9066,13 @@
         <v>3</v>
       </c>
       <c r="H92">
-        <v>98.01480183</v>
+        <v>96.16123299</v>
       </c>
       <c r="I92">
-        <v>0.3392907559</v>
+        <v>1.808688268</v>
       </c>
       <c r="J92">
-        <v>1.645907412</v>
+        <v>2.030078743</v>
       </c>
       <c r="K92">
         <v>86</v>
@@ -9141,13 +9129,13 @@
         <v>0</v>
       </c>
       <c r="AC92">
-        <v>0.002814361181</v>
+        <v>0.002693421288</v>
       </c>
       <c r="AD92">
-        <v>-0.002497197103</v>
+        <v>-0.002436355893</v>
       </c>
       <c r="AE92">
-        <v>-0.0003171640783</v>
+        <v>-0.0002570653951</v>
       </c>
     </row>
     <row r="93" spans="1:31">
@@ -9161,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1.14286889189592</v>
+        <v>1.13712240056478</v>
       </c>
       <c r="E93">
         <v>99</v>
@@ -9244,7 +9232,7 @@
     </row>
     <row r="94" spans="1:31">
       <c r="A94">
-        <v>887.249546</v>
+        <v>885.030002</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -9253,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>28.0819238708242</v>
+        <v>22.9675924284786</v>
       </c>
       <c r="E94">
         <v>85</v>
@@ -9265,13 +9253,13 @@
         <v>4</v>
       </c>
       <c r="H94">
-        <v>97.56185415</v>
+        <v>95.16017346</v>
       </c>
       <c r="I94">
-        <v>0.2518688747</v>
+        <v>2.19028451</v>
       </c>
       <c r="J94">
-        <v>2.186276977</v>
+        <v>2.649542033</v>
       </c>
       <c r="K94">
         <v>85</v>
@@ -9328,18 +9316,18 @@
         <v>0</v>
       </c>
       <c r="AC94">
-        <v>0.002225319703</v>
+        <v>0.002208250187</v>
       </c>
       <c r="AD94">
-        <v>-0.001904042087</v>
+        <v>-0.00191476261</v>
       </c>
       <c r="AE94">
-        <v>-0.000321277616</v>
+        <v>-0.0002934875771</v>
       </c>
     </row>
     <row r="95" spans="1:31">
       <c r="A95">
-        <v>874.955253</v>
+        <v>872.8975801</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -9348,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>36.5054582633965</v>
+        <v>27.1770437929066</v>
       </c>
       <c r="E95">
         <v>84</v>
@@ -9360,13 +9348,13 @@
         <v>5</v>
       </c>
       <c r="H95">
-        <v>97.04283168000001</v>
+        <v>93.94478709000001</v>
       </c>
       <c r="I95">
-        <v>0.1904282498</v>
+        <v>2.755327462</v>
       </c>
       <c r="J95">
-        <v>2.766740073</v>
+        <v>3.299885452</v>
       </c>
       <c r="K95">
         <v>84</v>
@@ -9423,13 +9411,13 @@
         <v>0</v>
       </c>
       <c r="AC95">
-        <v>0.001778452791</v>
+        <v>0.001827889609</v>
       </c>
       <c r="AD95">
-        <v>-0.001473956701</v>
+        <v>-0.001515419176</v>
       </c>
       <c r="AE95">
-        <v>-0.00030449609</v>
+        <v>-0.0003124704334</v>
       </c>
     </row>
     <row r="96" spans="1:31">
@@ -9443,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>15.5510689711452</v>
+        <v>15.5916593997198</v>
       </c>
       <c r="E96">
         <v>88</v>
@@ -9526,7 +9514,7 @@
     </row>
     <row r="97" spans="1:31">
       <c r="A97">
-        <v>901.873339</v>
+        <v>901.6215653</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -9535,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>15.9352168309411</v>
+        <v>15.6428737689923</v>
       </c>
       <c r="E97">
         <v>87</v>
@@ -9547,13 +9535,13 @@
         <v>1</v>
       </c>
       <c r="H97">
-        <v>98.63524141000001</v>
+        <v>97.71813281</v>
       </c>
       <c r="I97">
-        <v>0.7795704832</v>
+        <v>1.507685497</v>
       </c>
       <c r="J97">
-        <v>0.5851881115999999</v>
+        <v>0.774181688</v>
       </c>
       <c r="K97">
         <v>87</v>
@@ -9610,18 +9598,18 @@
         <v>0</v>
       </c>
       <c r="AC97">
-        <v>0.003628621432</v>
+        <v>0.003415626095</v>
       </c>
       <c r="AD97">
-        <v>-0.003499254151</v>
+        <v>-0.003343670192</v>
       </c>
       <c r="AE97">
-        <v>-0.0001293672807</v>
+        <v>-7.19559032E-05</v>
       </c>
     </row>
     <row r="98" spans="1:31">
       <c r="A98">
-        <v>899.3892488</v>
+        <v>898.1929652</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -9630,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>18.4975745566733</v>
+        <v>17.3788458445362</v>
       </c>
       <c r="E98">
         <v>86</v>
@@ -9642,13 +9630,13 @@
         <v>2</v>
       </c>
       <c r="H98">
-        <v>98.36754424999999</v>
+        <v>96.83156337</v>
       </c>
       <c r="I98">
-        <v>0.528324161</v>
+        <v>1.743532605</v>
       </c>
       <c r="J98">
-        <v>1.104131593</v>
+        <v>1.424904021</v>
       </c>
       <c r="K98">
         <v>86</v>
@@ -9705,18 +9693,18 @@
         <v>0</v>
       </c>
       <c r="AC98">
-        <v>0.003322719148</v>
+        <v>0.003107787487</v>
       </c>
       <c r="AD98">
-        <v>-0.003082039812</v>
+        <v>-0.002942802518</v>
       </c>
       <c r="AE98">
-        <v>-0.0002406793357</v>
+        <v>-0.0001649849687</v>
       </c>
     </row>
     <row r="99" spans="1:31">
       <c r="A99">
-        <v>893.3034496</v>
+        <v>891.3065585000001</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -9725,7 +9713,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>23.7344549391707</v>
+        <v>20.6600414617144</v>
       </c>
       <c r="E99">
         <v>85</v>
@@ -9737,13 +9725,13 @@
         <v>3</v>
       </c>
       <c r="H99">
-        <v>97.99805424</v>
+        <v>95.88697019999999</v>
       </c>
       <c r="I99">
-        <v>0.379844976</v>
+        <v>2.064920826</v>
       </c>
       <c r="J99">
-        <v>1.622100781</v>
+        <v>2.048108974</v>
       </c>
       <c r="K99">
         <v>85</v>
@@ -9800,18 +9788,18 @@
         <v>0</v>
       </c>
       <c r="AC99">
-        <v>0.002721988894</v>
+        <v>0.002629163948</v>
       </c>
       <c r="AD99">
-        <v>-0.002433452563</v>
+        <v>-0.002399312379</v>
       </c>
       <c r="AE99">
-        <v>-0.0002885363315</v>
+        <v>-0.0002298515693</v>
       </c>
     </row>
     <row r="100" spans="1:31">
       <c r="A100">
-        <v>883.731384</v>
+        <v>881.4217954</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -9820,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>31.2289421644214</v>
+        <v>24.6854742139613</v>
       </c>
       <c r="E100">
         <v>84</v>
@@ -9832,13 +9820,13 @@
         <v>4</v>
       </c>
       <c r="H100">
-        <v>97.5469016</v>
+        <v>94.77167162000001</v>
       </c>
       <c r="I100">
-        <v>0.2825340017</v>
+        <v>2.540140255</v>
       </c>
       <c r="J100">
-        <v>2.170564402</v>
+        <v>2.688188126</v>
       </c>
       <c r="K100">
         <v>84</v>
@@ -9895,18 +9883,18 @@
         <v>0</v>
       </c>
       <c r="AC100">
-        <v>0.002157232856</v>
+        <v>0.002178676782</v>
       </c>
       <c r="AD100">
-        <v>-0.001865928491</v>
+        <v>-0.001913373444</v>
       </c>
       <c r="AE100">
-        <v>-0.0002913043656</v>
+        <v>-0.0002653033382</v>
       </c>
     </row>
     <row r="101" spans="1:31">
       <c r="A101">
-        <v>870.9137131</v>
+        <v>868.9847791</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -9915,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>40.2745727335574</v>
+        <v>28.4177495284799</v>
       </c>
       <c r="E101">
         <v>83</v>
@@ -9927,13 +9915,13 @@
         <v>5</v>
       </c>
       <c r="H101">
-        <v>97.02290237</v>
+        <v>93.39391963999999</v>
       </c>
       <c r="I101">
-        <v>0.2135813232</v>
+        <v>3.244357416</v>
       </c>
       <c r="J101">
-        <v>2.763516302</v>
+        <v>3.361722946</v>
       </c>
       <c r="K101">
         <v>83</v>
@@ -9990,13 +9978,13 @@
         <v>0</v>
       </c>
       <c r="AC101">
-        <v>0.001732456579</v>
+        <v>0.001827440654</v>
       </c>
       <c r="AD101">
-        <v>-0.001456167657</v>
+        <v>-0.001539416683</v>
       </c>
       <c r="AE101">
-        <v>-0.0002762889215</v>
+        <v>-0.0002880239706</v>
       </c>
     </row>
     <row r="102" spans="1:31">
@@ -10010,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>17.0923834810786</v>
+        <v>17.134756985666</v>
       </c>
       <c r="E102">
         <v>87</v>
@@ -10093,7 +10081,7 @@
     </row>
     <row r="103" spans="1:31">
       <c r="A103">
-        <v>899.0113021</v>
+        <v>898.6275143</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -10102,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>17.6055379406349</v>
+        <v>17.3107500027609</v>
       </c>
       <c r="E103">
         <v>86</v>
@@ -10114,13 +10102,13 @@
         <v>1</v>
       </c>
       <c r="H103">
-        <v>98.5748731</v>
+        <v>97.56471984</v>
       </c>
       <c r="I103">
-        <v>0.8589714878</v>
+        <v>1.665112145</v>
       </c>
       <c r="J103">
-        <v>0.566155408</v>
+        <v>0.7701680128</v>
       </c>
       <c r="K103">
         <v>86</v>
@@ -10177,18 +10165,18 @@
         <v>0</v>
       </c>
       <c r="AC103">
-        <v>0.00355055092</v>
+        <v>0.00333107466</v>
       </c>
       <c r="AD103">
-        <v>-0.0034280516</v>
+        <v>-0.003264881033</v>
       </c>
       <c r="AE103">
-        <v>-0.0001224993192</v>
+        <v>-6.619362732999999E-05</v>
       </c>
     </row>
     <row r="104" spans="1:31">
       <c r="A104">
-        <v>930.90018</v>
+        <v>930.9992655999999</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -10197,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>1.31906476837623</v>
+        <v>1.19113799755578</v>
       </c>
       <c r="E104">
         <v>98</v>
@@ -10209,13 +10197,13 @@
         <v>1</v>
       </c>
       <c r="H104">
-        <v>99.08617044</v>
+        <v>99.01415344</v>
       </c>
       <c r="I104">
-        <v>0.05574880139</v>
+        <v>0.1102164266</v>
       </c>
       <c r="J104">
-        <v>0.8580807544</v>
+        <v>0.8756301344</v>
       </c>
       <c r="K104">
         <v>98</v>
@@ -10272,18 +10260,18 @@
         <v>0</v>
       </c>
       <c r="AC104">
-        <v>0.00400825365</v>
+        <v>0.004123646983</v>
       </c>
       <c r="AD104">
-        <v>-0.003485268449</v>
+        <v>-0.003618844944</v>
       </c>
       <c r="AE104">
-        <v>-0.0005229852011000001</v>
+        <v>-0.0005048020395</v>
       </c>
     </row>
     <row r="105" spans="1:31">
       <c r="A105">
-        <v>896.4325869</v>
+        <v>895.0395523</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -10292,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>20.5916452851995</v>
+        <v>19.2081765849054</v>
       </c>
       <c r="E105">
         <v>85</v>
@@ -10304,13 +10292,13 @@
         <v>2</v>
       </c>
       <c r="H105">
-        <v>98.33541115</v>
+        <v>96.61832196</v>
       </c>
       <c r="I105">
-        <v>0.5853602645</v>
+        <v>1.952091287</v>
       </c>
       <c r="J105">
-        <v>1.079228586</v>
+        <v>1.429586752</v>
       </c>
       <c r="K105">
         <v>85</v>
@@ -10367,18 +10355,18 @@
         <v>0</v>
       </c>
       <c r="AC105">
-        <v>0.0032175906</v>
+        <v>0.003016753796</v>
       </c>
       <c r="AD105">
-        <v>-0.002995432238</v>
+        <v>-0.002868662179</v>
       </c>
       <c r="AE105">
-        <v>-0.0002221583621</v>
+        <v>-0.0001480916177</v>
       </c>
     </row>
     <row r="106" spans="1:31">
       <c r="A106">
-        <v>890.0581449</v>
+        <v>887.8904530999999</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -10387,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>26.4503883809382</v>
+        <v>22.5369191974516</v>
       </c>
       <c r="E106">
         <v>84</v>
@@ -10399,13 +10387,13 @@
         <v>3</v>
       </c>
       <c r="H106">
-        <v>97.97791718000001</v>
+        <v>95.58131351999999</v>
       </c>
       <c r="I106">
-        <v>0.4224774558</v>
+        <v>2.349042767</v>
       </c>
       <c r="J106">
-        <v>1.599605368</v>
+        <v>2.069643711</v>
       </c>
       <c r="K106">
         <v>84</v>
@@ -10462,18 +10450,18 @@
         <v>0</v>
       </c>
       <c r="AC106">
-        <v>0.002625771515</v>
+        <v>0.002564637814</v>
       </c>
       <c r="AD106">
-        <v>-0.002362719174</v>
+        <v>-0.002358638008</v>
       </c>
       <c r="AE106">
-        <v>-0.000263052341</v>
+        <v>-0.0002059998061</v>
       </c>
     </row>
     <row r="107" spans="1:31">
       <c r="A107">
-        <v>880.0387385</v>
+        <v>877.6961721</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -10482,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>34.6298400632951</v>
+        <v>26.3236884919488</v>
       </c>
       <c r="E107">
         <v>83</v>
@@ -10494,13 +10482,13 @@
         <v>4</v>
       </c>
       <c r="H107">
-        <v>97.52877535</v>
+        <v>94.3301307</v>
       </c>
       <c r="I107">
-        <v>0.3148160986</v>
+        <v>2.938031352</v>
       </c>
       <c r="J107">
-        <v>2.156408551</v>
+        <v>2.731837944</v>
       </c>
       <c r="K107">
         <v>83</v>
@@ -10557,18 +10545,18 @@
         <v>0</v>
       </c>
       <c r="AC107">
-        <v>0.002085540866</v>
+        <v>0.002149574836</v>
       </c>
       <c r="AD107">
-        <v>-0.001820917058</v>
+        <v>-0.001908998168</v>
       </c>
       <c r="AE107">
-        <v>-0.0002646238078</v>
+        <v>-0.0002405766683</v>
       </c>
     </row>
     <row r="108" spans="1:31">
       <c r="A108">
-        <v>866.6599303</v>
+        <v>864.9804343</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -10577,7 +10565,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>44.3304020327493</v>
+        <v>29.3895148307018</v>
       </c>
       <c r="E108">
         <v>82</v>
@@ -10589,13 +10577,13 @@
         <v>5</v>
       </c>
       <c r="H108">
-        <v>96.9998557</v>
+        <v>92.75876957</v>
       </c>
       <c r="I108">
-        <v>0.2378875392</v>
+        <v>3.811692036</v>
       </c>
       <c r="J108">
-        <v>2.76225676</v>
+        <v>3.429538391</v>
       </c>
       <c r="K108">
         <v>82</v>
@@ -10652,13 +10640,13 @@
         <v>0</v>
       </c>
       <c r="AC108">
-        <v>0.001682852607</v>
+        <v>0.001829491642</v>
       </c>
       <c r="AD108">
-        <v>-0.001431812178</v>
+        <v>-0.001562453165</v>
       </c>
       <c r="AE108">
-        <v>-0.0002510404284</v>
+        <v>-0.0002670384763</v>
       </c>
     </row>
     <row r="109" spans="1:31">
@@ -10672,7 +10660,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>18.6843485881649</v>
+        <v>18.7368544124464</v>
       </c>
       <c r="E109">
         <v>86</v>
@@ -10755,7 +10743,7 @@
     </row>
     <row r="110" spans="1:31">
       <c r="A110">
-        <v>896.0855639</v>
+        <v>895.5588545000001</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -10764,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>19.3682875212275</v>
+        <v>19.0609296784062</v>
       </c>
       <c r="E110">
         <v>85</v>
@@ -10776,13 +10764,13 @@
         <v>1</v>
       </c>
       <c r="H110">
-        <v>98.51058473000001</v>
+        <v>97.40178684999999</v>
       </c>
       <c r="I110">
-        <v>0.9414656135</v>
+        <v>1.83102772</v>
       </c>
       <c r="J110">
-        <v>0.5479496564</v>
+        <v>0.7671854328</v>
       </c>
       <c r="K110">
         <v>85</v>
@@ -10839,18 +10827,18 @@
         <v>0</v>
       </c>
       <c r="AC110">
-        <v>0.003466787271</v>
+        <v>0.003244822388</v>
       </c>
       <c r="AD110">
-        <v>-0.003350790182</v>
+        <v>-0.003183914598</v>
       </c>
       <c r="AE110">
-        <v>-0.000115997089</v>
+        <v>-6.09077898E-05</v>
       </c>
     </row>
     <row r="111" spans="1:31">
       <c r="A111">
-        <v>893.375548</v>
+        <v>891.7839563</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -10859,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>22.8472156988598</v>
+        <v>21.1135438648929</v>
       </c>
       <c r="E111">
         <v>84</v>
@@ -10871,13 +10859,13 @@
         <v>2</v>
       </c>
       <c r="H111">
-        <v>98.29947084</v>
+        <v>96.38505646999999</v>
       </c>
       <c r="I111">
-        <v>0.6450828872</v>
+        <v>2.178389189</v>
       </c>
       <c r="J111">
-        <v>1.055446274</v>
+        <v>1.436554341</v>
       </c>
       <c r="K111">
         <v>84</v>
@@ -10934,18 +10922,18 @@
         <v>0</v>
       </c>
       <c r="AC111">
-        <v>0.003108658626</v>
+        <v>0.002926259059</v>
       </c>
       <c r="AD111">
-        <v>-0.002903321344</v>
+        <v>-0.002793149006</v>
       </c>
       <c r="AE111">
-        <v>-0.0002053372824</v>
+        <v>-0.0001331100525</v>
       </c>
     </row>
     <row r="112" spans="1:31">
       <c r="A112">
-        <v>886.6700003</v>
+        <v>884.356357</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -10954,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>29.3876991883469</v>
+        <v>24.4222020049872</v>
       </c>
       <c r="E112">
         <v>83</v>
@@ -10966,13 +10954,13 @@
         <v>3</v>
       </c>
       <c r="H112">
-        <v>97.95426191999999</v>
+        <v>95.23851877</v>
       </c>
       <c r="I112">
-        <v>0.467325907</v>
+        <v>2.666434941</v>
       </c>
       <c r="J112">
-        <v>1.578412176</v>
+        <v>2.095046293</v>
       </c>
       <c r="K112">
         <v>83</v>
@@ -11029,18 +11017,18 @@
         <v>0</v>
       </c>
       <c r="AC112">
-        <v>0.002527446492</v>
+        <v>0.002501510483</v>
       </c>
       <c r="AD112">
-        <v>-0.002287192956</v>
+        <v>-0.002316563142</v>
       </c>
       <c r="AE112">
-        <v>-0.0002402535359</v>
+        <v>-0.0001849473402</v>
       </c>
     </row>
     <row r="113" spans="1:31">
       <c r="A113">
-        <v>876.1614855</v>
+        <v>873.8585749</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -11049,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>38.2996181672629</v>
+        <v>27.8237192920301</v>
       </c>
       <c r="E113">
         <v>82</v>
@@ -11061,13 +11049,13 @@
         <v>4</v>
       </c>
       <c r="H113">
-        <v>97.50736067</v>
+        <v>93.82491563000001</v>
       </c>
       <c r="I113">
-        <v>0.3488049671</v>
+        <v>3.394116629</v>
       </c>
       <c r="J113">
-        <v>2.143834363</v>
+        <v>2.780967743</v>
       </c>
       <c r="K113">
         <v>82</v>
@@ -11124,18 +11112,18 @@
         <v>0</v>
       </c>
       <c r="AC113">
-        <v>0.002011804777</v>
+        <v>0.002123053561</v>
       </c>
       <c r="AD113">
-        <v>-0.001771013514</v>
+        <v>-0.001904207628</v>
       </c>
       <c r="AE113">
-        <v>-0.0002407912624</v>
+        <v>-0.0002188459328</v>
       </c>
     </row>
     <row r="114" spans="1:31">
       <c r="A114">
-        <v>862.1833003</v>
+        <v>860.9024219</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -11144,7 +11132,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>48.6868442944742</v>
+        <v>30.0015446946585</v>
       </c>
       <c r="E114">
         <v>81</v>
@@ -11156,13 +11144,13 @@
         <v>5</v>
       </c>
       <c r="H114">
-        <v>96.97357848</v>
+        <v>92.02254352</v>
       </c>
       <c r="I114">
-        <v>0.2633875032</v>
+        <v>4.473907248</v>
       </c>
       <c r="J114">
-        <v>2.763034016</v>
+        <v>3.503549233</v>
       </c>
       <c r="K114">
         <v>81</v>
@@ -11219,18 +11207,18 @@
         <v>0</v>
       </c>
       <c r="AC114">
-        <v>0.001630925405</v>
+        <v>0.001836615978</v>
       </c>
       <c r="AD114">
-        <v>-0.001402540863</v>
+        <v>-0.001587283063</v>
       </c>
       <c r="AE114">
-        <v>-0.0002283845421</v>
+        <v>-0.0002493329156</v>
       </c>
     </row>
     <row r="115" spans="1:31">
       <c r="A115">
-        <v>927.5006084</v>
+        <v>927.5300003</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -11239,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>2.31117648856398</v>
+        <v>2.17780621576832</v>
       </c>
       <c r="E115">
         <v>97</v>
@@ -11251,13 +11239,13 @@
         <v>2</v>
       </c>
       <c r="H115">
-        <v>98.50401189</v>
+        <v>98.39807775</v>
       </c>
       <c r="I115">
-        <v>0.03544621377</v>
+        <v>0.1146909363</v>
       </c>
       <c r="J115">
-        <v>1.460541892</v>
+        <v>1.487231317</v>
       </c>
       <c r="K115">
         <v>97</v>
@@ -11314,13 +11302,13 @@
         <v>0</v>
       </c>
       <c r="AC115">
-        <v>0.003207686439</v>
+        <v>0.003160614981</v>
       </c>
       <c r="AD115">
-        <v>-0.002057838778</v>
+        <v>-0.002002068013</v>
       </c>
       <c r="AE115">
-        <v>-0.001149847661</v>
+        <v>-0.001158546968</v>
       </c>
     </row>
     <row r="116" spans="1:31">
@@ -11334,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>20.3179613146173</v>
+        <v>20.3819792846892</v>
       </c>
       <c r="E116">
         <v>85</v>
@@ -11417,7 +11405,7 @@
     </row>
     <row r="117" spans="1:31">
       <c r="A117">
-        <v>893.0892232</v>
+        <v>892.4103041</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -11426,7 +11414,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>21.2420866318474</v>
+        <v>20.89765254404</v>
       </c>
       <c r="E117">
         <v>84</v>
@@ -11438,13 +11426,13 @@
         <v>1</v>
       </c>
       <c r="H117">
-        <v>98.44214114</v>
+        <v>97.22802969</v>
       </c>
       <c r="I117">
-        <v>1.027317673</v>
+        <v>2.006673218</v>
       </c>
       <c r="J117">
-        <v>0.5305411864</v>
+        <v>0.7652970898</v>
       </c>
       <c r="K117">
         <v>84</v>
@@ -11501,18 +11489,18 @@
         <v>0</v>
       </c>
       <c r="AC117">
-        <v>0.003378049268</v>
+        <v>0.003157365447</v>
       </c>
       <c r="AD117">
-        <v>-0.003268239965</v>
+        <v>-0.003101350654</v>
       </c>
       <c r="AE117">
-        <v>-0.0001098093027</v>
+        <v>-5.601479333E-05</v>
       </c>
     </row>
     <row r="118" spans="1:31">
       <c r="A118">
-        <v>890.2095371</v>
+        <v>888.4217849</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -11521,7 +11509,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>25.2786535121591</v>
+        <v>23.0876701734823</v>
       </c>
       <c r="E118">
         <v>83</v>
@@ -11533,13 +11521,13 @@
         <v>2</v>
       </c>
       <c r="H118">
-        <v>98.2595481</v>
+        <v>96.12843927</v>
       </c>
       <c r="I118">
-        <v>0.7076945296</v>
+        <v>2.425537745</v>
       </c>
       <c r="J118">
-        <v>1.032757371</v>
+        <v>1.446022982</v>
       </c>
       <c r="K118">
         <v>83</v>
@@ -11596,18 +11584,18 @@
         <v>0</v>
       </c>
       <c r="AC118">
-        <v>0.002997269524</v>
+        <v>0.002837239989</v>
       </c>
       <c r="AD118">
-        <v>-0.002807289078</v>
+        <v>-0.002717533548</v>
       </c>
       <c r="AE118">
-        <v>-0.0001899804457</v>
+        <v>-0.0001197064412</v>
       </c>
     </row>
     <row r="119" spans="1:31">
       <c r="A119">
-        <v>883.1293306</v>
+        <v>880.7039823</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -11616,7 +11604,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>32.5616746344417</v>
+        <v>26.2829533252974</v>
       </c>
       <c r="E119">
         <v>82</v>
@@ -11628,13 +11616,13 @@
         <v>3</v>
       </c>
       <c r="H119">
-        <v>97.92694569</v>
+        <v>94.85139655</v>
       </c>
       <c r="I119">
-        <v>0.5145398231</v>
+        <v>3.023861196</v>
       </c>
       <c r="J119">
-        <v>1.55851449</v>
+        <v>2.124742255</v>
       </c>
       <c r="K119">
         <v>82</v>
@@ -11691,18 +11679,18 @@
         <v>0</v>
       </c>
       <c r="AC119">
-        <v>0.002428398217</v>
+        <v>0.002441246262</v>
       </c>
       <c r="AD119">
-        <v>-0.002208623188</v>
+        <v>-0.002275003142</v>
       </c>
       <c r="AE119">
-        <v>-0.0002197750291</v>
+        <v>-0.0001662431199</v>
       </c>
     </row>
     <row r="120" spans="1:31">
       <c r="A120">
-        <v>872.0891884</v>
+        <v>869.917705</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -11711,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>42.2535001411973</v>
+        <v>29.1112835062281</v>
       </c>
       <c r="E120">
         <v>81</v>
@@ -11723,13 +11711,13 @@
         <v>4</v>
       </c>
       <c r="H120">
-        <v>97.48253281</v>
+        <v>93.24270498</v>
       </c>
       <c r="I120">
-        <v>0.3845953365</v>
+        <v>3.921213359</v>
       </c>
       <c r="J120">
-        <v>2.132871854</v>
+        <v>2.836081661</v>
       </c>
       <c r="K120">
         <v>81</v>
@@ -11786,18 +11774,18 @@
         <v>0</v>
       </c>
       <c r="AC120">
-        <v>0.001937231567</v>
+        <v>0.002101273005</v>
       </c>
       <c r="AD120">
-        <v>-0.001717794966</v>
+        <v>-0.001901522943</v>
       </c>
       <c r="AE120">
-        <v>-0.0002194366001</v>
+        <v>-0.0001997500627</v>
       </c>
     </row>
     <row r="121" spans="1:31">
       <c r="A121">
-        <v>857.4729081</v>
+        <v>856.7747893</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -11806,7 +11794,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>53.3578592180321</v>
+        <v>30.151557601851</v>
       </c>
       <c r="E121">
         <v>80</v>
@@ -11818,13 +11806,13 @@
         <v>5</v>
       </c>
       <c r="H121">
-        <v>96.94395016</v>
+        <v>91.16529</v>
       </c>
       <c r="I121">
-        <v>0.2901198704</v>
+        <v>5.250943708</v>
       </c>
       <c r="J121">
-        <v>2.76592997</v>
+        <v>3.583766294</v>
       </c>
       <c r="K121">
         <v>80</v>
@@ -11881,13 +11869,13 @@
         <v>0</v>
       </c>
       <c r="AC121">
-        <v>0.00157768276</v>
+        <v>0.001851742876</v>
       </c>
       <c r="AD121">
-        <v>-0.001369675676</v>
+        <v>-0.001616871975</v>
       </c>
       <c r="AE121">
-        <v>-0.0002080070838</v>
+        <v>-0.0002348709011</v>
       </c>
     </row>
     <row r="122" spans="1:31">
@@ -11901,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>22.0362209619515</v>
+        <v>22.1131993766688</v>
       </c>
       <c r="E122">
         <v>84</v>
@@ -11984,7 +11972,7 @@
     </row>
     <row r="123" spans="1:31">
       <c r="A123">
-        <v>890.0151249</v>
+        <v>889.1764805</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -11993,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>23.2386503085278</v>
+        <v>22.8243020672295</v>
       </c>
       <c r="E123">
         <v>83</v>
@@ -12005,13 +11993,13 @@
         <v>1</v>
       </c>
       <c r="H123">
-        <v>98.36927710000001</v>
+        <v>97.04191113</v>
       </c>
       <c r="I123">
-        <v>1.116821939</v>
+        <v>2.193510855</v>
       </c>
       <c r="J123">
-        <v>0.5139009638000001</v>
+        <v>0.7645780165</v>
       </c>
       <c r="K123">
         <v>83</v>
@@ -12068,18 +12056,18 @@
         <v>0</v>
       </c>
       <c r="AC123">
-        <v>0.003285085265</v>
+        <v>0.00306920105</v>
       </c>
       <c r="AD123">
-        <v>-0.00318118298</v>
+        <v>-0.003017749448</v>
       </c>
       <c r="AE123">
-        <v>-0.000103902285</v>
+        <v>-5.145160177E-05</v>
       </c>
     </row>
     <row r="124" spans="1:31">
       <c r="A124">
-        <v>886.9256819</v>
+        <v>884.9490695</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -12088,7 +12076,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>27.9006218233147</v>
+        <v>25.1188951371042</v>
       </c>
       <c r="E124">
         <v>82</v>
@@ -12100,13 +12088,13 @@
         <v>2</v>
       </c>
       <c r="H124">
-        <v>98.21544600999999</v>
+        <v>95.84436809</v>
       </c>
       <c r="I124">
-        <v>0.7734183578</v>
+        <v>2.697380613</v>
       </c>
       <c r="J124">
-        <v>1.011135633</v>
+        <v>1.458251301</v>
       </c>
       <c r="K124">
         <v>82</v>
@@ -12163,18 +12151,18 @@
         <v>0</v>
       </c>
       <c r="AC124">
-        <v>0.002884608044</v>
+        <v>0.002750543579</v>
       </c>
       <c r="AD124">
-        <v>-0.002708700274</v>
+        <v>-0.002642925832</v>
       </c>
       <c r="AE124">
-        <v>-0.0001759077702</v>
+        <v>-0.0001076177476</v>
       </c>
     </row>
     <row r="125" spans="1:31">
       <c r="A125">
-        <v>879.4261441</v>
+        <v>876.9347752</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -12183,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>35.9884220413109</v>
+        <v>28.078631091698</v>
       </c>
       <c r="E125">
         <v>81</v>
@@ -12195,13 +12183,13 @@
         <v>3</v>
       </c>
       <c r="H125">
-        <v>97.89581019000001</v>
+        <v>94.4108461</v>
       </c>
       <c r="I125">
-        <v>0.5642817272</v>
+        <v>3.429923957</v>
       </c>
       <c r="J125">
-        <v>1.53990808</v>
+        <v>2.159229941</v>
       </c>
       <c r="K125">
         <v>81</v>
@@ -12258,18 +12246,18 @@
         <v>0</v>
       </c>
       <c r="AC125">
-        <v>0.002329704698</v>
+        <v>0.002385234136</v>
       </c>
       <c r="AD125">
-        <v>-0.002128386017</v>
+        <v>-0.002235715366</v>
       </c>
       <c r="AE125">
-        <v>-0.0002013186805</v>
+        <v>-0.0001495187696</v>
       </c>
     </row>
     <row r="126" spans="1:31">
       <c r="A126">
-        <v>922.073884</v>
+        <v>921.990078</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -12278,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>4.33427787887098</v>
+        <v>4.22746677403689</v>
       </c>
       <c r="E126">
         <v>96</v>
@@ -12290,13 +12278,13 @@
         <v>3</v>
       </c>
       <c r="H126">
-        <v>98.01641563</v>
+        <v>97.88902622000001</v>
       </c>
       <c r="I126">
-        <v>0.02430416582</v>
+        <v>0.1194889674</v>
       </c>
       <c r="J126">
-        <v>1.959280203</v>
+        <v>1.991484813</v>
       </c>
       <c r="K126">
         <v>96</v>
@@ -12353,18 +12341,18 @@
         <v>0</v>
       </c>
       <c r="AC126">
-        <v>0.002307382697</v>
+        <v>0.002215568945</v>
       </c>
       <c r="AD126">
-        <v>-0.001116766788</v>
+        <v>-0.001032941567</v>
       </c>
       <c r="AE126">
-        <v>-0.001190615909</v>
+        <v>-0.001182627378</v>
       </c>
     </row>
     <row r="127" spans="1:31">
       <c r="A127">
-        <v>933.4727259</v>
+        <v>933.473</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -12373,7 +12361,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>1.01999999999998</v>
+        <v>1.02027409999994</v>
       </c>
       <c r="E127">
         <v>100</v>
